--- a/Work/MS BRIBox/Database/Copy of PENGADAAN_RO_PADANG(1).xlsx
+++ b/Work/MS BRIBox/Database/Copy of PENGADAAN_RO_PADANG(1).xlsx
@@ -12,7 +12,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="benBH1/QFsUZzhWE4557c/iXfuyGCKxfChK1VMzx0jE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="Piy/olnfyY0h+xys9CUmA+tC9kFtQpONvunmYTB153E="/>
     </ext>
   </extLst>
 </workbook>
@@ -4739,7 +4739,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -7424,7 +7423,7 @@
       <c r="AW11" s="7"/>
       <c r="AX11" s="7"/>
     </row>
-    <row r="12" ht="20.25" hidden="1" customHeight="1">
+    <row r="12" ht="20.25" customHeight="1">
       <c r="A12" s="8">
         <v>782.0</v>
       </c>
@@ -7528,7 +7527,7 @@
       <c r="AW12" s="7"/>
       <c r="AX12" s="7"/>
     </row>
-    <row r="13" ht="20.25" hidden="1" customHeight="1">
+    <row r="13" ht="20.25" customHeight="1">
       <c r="A13" s="12">
         <v>783.0</v>
       </c>
@@ -7632,7 +7631,7 @@
       <c r="AW13" s="7"/>
       <c r="AX13" s="7"/>
     </row>
-    <row r="14" ht="20.25" hidden="1" customHeight="1">
+    <row r="14" ht="20.25" customHeight="1">
       <c r="A14" s="8">
         <v>784.0</v>
       </c>
@@ -7736,7 +7735,7 @@
       <c r="AW14" s="7"/>
       <c r="AX14" s="7"/>
     </row>
-    <row r="15" ht="20.25" hidden="1" customHeight="1">
+    <row r="15" ht="20.25" customHeight="1">
       <c r="A15" s="12">
         <v>785.0</v>
       </c>
@@ -7840,7 +7839,7 @@
       <c r="AW15" s="7"/>
       <c r="AX15" s="7"/>
     </row>
-    <row r="16" ht="20.25" hidden="1" customHeight="1">
+    <row r="16" ht="20.25" customHeight="1">
       <c r="A16" s="8">
         <v>786.0</v>
       </c>
@@ -7944,7 +7943,7 @@
       <c r="AW16" s="7"/>
       <c r="AX16" s="7"/>
     </row>
-    <row r="17" ht="20.25" hidden="1" customHeight="1">
+    <row r="17" ht="20.25" customHeight="1">
       <c r="A17" s="12">
         <v>787.0</v>
       </c>
@@ -8048,7 +8047,7 @@
       <c r="AW17" s="7"/>
       <c r="AX17" s="7"/>
     </row>
-    <row r="18" ht="20.25" hidden="1" customHeight="1">
+    <row r="18" ht="20.25" customHeight="1">
       <c r="A18" s="8">
         <v>788.0</v>
       </c>
@@ -8152,7 +8151,7 @@
       <c r="AW18" s="7"/>
       <c r="AX18" s="7"/>
     </row>
-    <row r="19" ht="20.25" hidden="1" customHeight="1">
+    <row r="19" ht="20.25" customHeight="1">
       <c r="A19" s="12">
         <v>789.0</v>
       </c>
@@ -8256,7 +8255,7 @@
       <c r="AW19" s="7"/>
       <c r="AX19" s="7"/>
     </row>
-    <row r="20" ht="20.25" hidden="1" customHeight="1">
+    <row r="20" ht="20.25" customHeight="1">
       <c r="A20" s="8">
         <v>790.0</v>
       </c>
@@ -8360,7 +8359,7 @@
       <c r="AW20" s="7"/>
       <c r="AX20" s="7"/>
     </row>
-    <row r="21" ht="20.25" hidden="1" customHeight="1">
+    <row r="21" ht="20.25" customHeight="1">
       <c r="A21" s="12">
         <v>791.0</v>
       </c>
@@ -8464,7 +8463,7 @@
       <c r="AW21" s="7"/>
       <c r="AX21" s="7"/>
     </row>
-    <row r="22" ht="20.25" hidden="1" customHeight="1">
+    <row r="22" ht="20.25" customHeight="1">
       <c r="A22" s="8">
         <v>792.0</v>
       </c>
@@ -8568,7 +8567,7 @@
       <c r="AW22" s="7"/>
       <c r="AX22" s="7"/>
     </row>
-    <row r="23" ht="20.25" hidden="1" customHeight="1">
+    <row r="23" ht="20.25" customHeight="1">
       <c r="A23" s="12">
         <v>793.0</v>
       </c>
@@ -8672,7 +8671,7 @@
       <c r="AW23" s="7"/>
       <c r="AX23" s="7"/>
     </row>
-    <row r="24" ht="20.25" hidden="1" customHeight="1">
+    <row r="24" ht="20.25" customHeight="1">
       <c r="A24" s="8">
         <v>794.0</v>
       </c>
@@ -8776,7 +8775,7 @@
       <c r="AW24" s="7"/>
       <c r="AX24" s="7"/>
     </row>
-    <row r="25" ht="20.25" hidden="1" customHeight="1">
+    <row r="25" ht="20.25" customHeight="1">
       <c r="A25" s="12">
         <v>795.0</v>
       </c>
@@ -8880,7 +8879,7 @@
       <c r="AW25" s="7"/>
       <c r="AX25" s="7"/>
     </row>
-    <row r="26" ht="20.25" hidden="1" customHeight="1">
+    <row r="26" ht="20.25" customHeight="1">
       <c r="A26" s="8">
         <v>796.0</v>
       </c>
@@ -8984,7 +8983,7 @@
       <c r="AW26" s="7"/>
       <c r="AX26" s="7"/>
     </row>
-    <row r="27" ht="20.25" hidden="1" customHeight="1">
+    <row r="27" ht="20.25" customHeight="1">
       <c r="A27" s="12">
         <v>797.0</v>
       </c>
@@ -9088,7 +9087,7 @@
       <c r="AW27" s="7"/>
       <c r="AX27" s="7"/>
     </row>
-    <row r="28" ht="20.25" hidden="1" customHeight="1">
+    <row r="28" ht="20.25" customHeight="1">
       <c r="A28" s="8">
         <v>798.0</v>
       </c>
@@ -9192,7 +9191,7 @@
       <c r="AW28" s="7"/>
       <c r="AX28" s="7"/>
     </row>
-    <row r="29" ht="20.25" hidden="1" customHeight="1">
+    <row r="29" ht="20.25" customHeight="1">
       <c r="A29" s="12">
         <v>799.0</v>
       </c>
@@ -9296,7 +9295,7 @@
       <c r="AW29" s="7"/>
       <c r="AX29" s="7"/>
     </row>
-    <row r="30" ht="20.25" hidden="1" customHeight="1">
+    <row r="30" ht="20.25" customHeight="1">
       <c r="A30" s="8">
         <v>800.0</v>
       </c>
@@ -9400,7 +9399,7 @@
       <c r="AW30" s="7"/>
       <c r="AX30" s="7"/>
     </row>
-    <row r="31" ht="20.25" hidden="1" customHeight="1">
+    <row r="31" ht="20.25" customHeight="1">
       <c r="A31" s="12">
         <v>801.0</v>
       </c>
@@ -9504,7 +9503,7 @@
       <c r="AW31" s="7"/>
       <c r="AX31" s="7"/>
     </row>
-    <row r="32" ht="20.25" hidden="1" customHeight="1">
+    <row r="32" ht="20.25" customHeight="1">
       <c r="A32" s="8">
         <v>802.0</v>
       </c>
@@ -9608,7 +9607,7 @@
       <c r="AW32" s="7"/>
       <c r="AX32" s="7"/>
     </row>
-    <row r="33" ht="20.25" hidden="1" customHeight="1">
+    <row r="33" ht="20.25" customHeight="1">
       <c r="A33" s="12">
         <v>803.0</v>
       </c>
@@ -9712,7 +9711,7 @@
       <c r="AW33" s="7"/>
       <c r="AX33" s="7"/>
     </row>
-    <row r="34" ht="20.25" hidden="1" customHeight="1">
+    <row r="34" ht="20.25" customHeight="1">
       <c r="A34" s="8">
         <v>804.0</v>
       </c>
@@ -9816,7 +9815,7 @@
       <c r="AW34" s="7"/>
       <c r="AX34" s="7"/>
     </row>
-    <row r="35" ht="20.25" hidden="1" customHeight="1">
+    <row r="35" ht="20.25" customHeight="1">
       <c r="A35" s="12">
         <v>805.0</v>
       </c>
@@ -9920,7 +9919,7 @@
       <c r="AW35" s="7"/>
       <c r="AX35" s="7"/>
     </row>
-    <row r="36" ht="20.25" hidden="1" customHeight="1">
+    <row r="36" ht="20.25" customHeight="1">
       <c r="A36" s="8">
         <v>806.0</v>
       </c>
@@ -10024,7 +10023,7 @@
       <c r="AW36" s="7"/>
       <c r="AX36" s="7"/>
     </row>
-    <row r="37" ht="20.25" hidden="1" customHeight="1">
+    <row r="37" ht="20.25" customHeight="1">
       <c r="A37" s="12">
         <v>807.0</v>
       </c>
@@ -10128,7 +10127,7 @@
       <c r="AW37" s="7"/>
       <c r="AX37" s="7"/>
     </row>
-    <row r="38" ht="20.25" hidden="1" customHeight="1">
+    <row r="38" ht="20.25" customHeight="1">
       <c r="A38" s="8">
         <v>808.0</v>
       </c>
@@ -10232,7 +10231,7 @@
       <c r="AW38" s="7"/>
       <c r="AX38" s="7"/>
     </row>
-    <row r="39" ht="20.25" hidden="1" customHeight="1">
+    <row r="39" ht="20.25" customHeight="1">
       <c r="A39" s="12">
         <v>809.0</v>
       </c>
@@ -10336,7 +10335,7 @@
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
     </row>
-    <row r="40" ht="20.25" hidden="1" customHeight="1">
+    <row r="40" ht="20.25" customHeight="1">
       <c r="A40" s="8">
         <v>810.0</v>
       </c>
@@ -10440,7 +10439,7 @@
       <c r="AW40" s="7"/>
       <c r="AX40" s="7"/>
     </row>
-    <row r="41" ht="20.25" hidden="1" customHeight="1">
+    <row r="41" ht="20.25" customHeight="1">
       <c r="A41" s="12">
         <v>811.0</v>
       </c>
@@ -10544,7 +10543,7 @@
       <c r="AW41" s="7"/>
       <c r="AX41" s="7"/>
     </row>
-    <row r="42" ht="20.25" hidden="1" customHeight="1">
+    <row r="42" ht="20.25" customHeight="1">
       <c r="A42" s="8">
         <v>812.0</v>
       </c>
@@ -10648,7 +10647,7 @@
       <c r="AW42" s="7"/>
       <c r="AX42" s="7"/>
     </row>
-    <row r="43" ht="20.25" hidden="1" customHeight="1">
+    <row r="43" ht="20.25" customHeight="1">
       <c r="A43" s="12">
         <v>813.0</v>
       </c>
@@ -10752,7 +10751,7 @@
       <c r="AW43" s="7"/>
       <c r="AX43" s="7"/>
     </row>
-    <row r="44" ht="20.25" hidden="1" customHeight="1">
+    <row r="44" ht="20.25" customHeight="1">
       <c r="A44" s="8">
         <v>814.0</v>
       </c>
@@ -10856,7 +10855,7 @@
       <c r="AW44" s="7"/>
       <c r="AX44" s="7"/>
     </row>
-    <row r="45" ht="20.25" hidden="1" customHeight="1">
+    <row r="45" ht="20.25" customHeight="1">
       <c r="A45" s="12">
         <v>815.0</v>
       </c>
@@ -10960,7 +10959,7 @@
       <c r="AW45" s="7"/>
       <c r="AX45" s="7"/>
     </row>
-    <row r="46" ht="20.25" hidden="1" customHeight="1">
+    <row r="46" ht="20.25" customHeight="1">
       <c r="A46" s="8">
         <v>816.0</v>
       </c>
@@ -11064,7 +11063,7 @@
       <c r="AW46" s="7"/>
       <c r="AX46" s="7"/>
     </row>
-    <row r="47" ht="20.25" hidden="1" customHeight="1">
+    <row r="47" ht="20.25" customHeight="1">
       <c r="A47" s="12">
         <v>817.0</v>
       </c>
@@ -11168,7 +11167,7 @@
       <c r="AW47" s="7"/>
       <c r="AX47" s="7"/>
     </row>
-    <row r="48" ht="20.25" hidden="1" customHeight="1">
+    <row r="48" ht="20.25" customHeight="1">
       <c r="A48" s="8">
         <v>818.0</v>
       </c>
@@ -11272,7 +11271,7 @@
       <c r="AW48" s="7"/>
       <c r="AX48" s="7"/>
     </row>
-    <row r="49" ht="20.25" hidden="1" customHeight="1">
+    <row r="49" ht="20.25" customHeight="1">
       <c r="A49" s="12">
         <v>819.0</v>
       </c>
@@ -11376,7 +11375,7 @@
       <c r="AW49" s="7"/>
       <c r="AX49" s="7"/>
     </row>
-    <row r="50" ht="20.25" hidden="1" customHeight="1">
+    <row r="50" ht="20.25" customHeight="1">
       <c r="A50" s="8">
         <v>820.0</v>
       </c>
@@ -11480,7 +11479,7 @@
       <c r="AW50" s="7"/>
       <c r="AX50" s="7"/>
     </row>
-    <row r="51" ht="20.25" hidden="1" customHeight="1">
+    <row r="51" ht="20.25" customHeight="1">
       <c r="A51" s="12">
         <v>821.0</v>
       </c>
@@ -11584,7 +11583,7 @@
       <c r="AW51" s="7"/>
       <c r="AX51" s="7"/>
     </row>
-    <row r="52" ht="20.25" hidden="1" customHeight="1">
+    <row r="52" ht="20.25" customHeight="1">
       <c r="A52" s="8">
         <v>822.0</v>
       </c>
@@ -11688,7 +11687,7 @@
       <c r="AW52" s="7"/>
       <c r="AX52" s="7"/>
     </row>
-    <row r="53" ht="20.25" hidden="1" customHeight="1">
+    <row r="53" ht="20.25" customHeight="1">
       <c r="A53" s="12">
         <v>823.0</v>
       </c>
@@ -11792,7 +11791,7 @@
       <c r="AW53" s="7"/>
       <c r="AX53" s="7"/>
     </row>
-    <row r="54" ht="20.25" hidden="1" customHeight="1">
+    <row r="54" ht="20.25" customHeight="1">
       <c r="A54" s="8">
         <v>824.0</v>
       </c>
@@ -11896,7 +11895,7 @@
       <c r="AW54" s="7"/>
       <c r="AX54" s="7"/>
     </row>
-    <row r="55" ht="20.25" hidden="1" customHeight="1">
+    <row r="55" ht="20.25" customHeight="1">
       <c r="A55" s="12">
         <v>825.0</v>
       </c>
@@ -12000,7 +11999,7 @@
       <c r="AW55" s="7"/>
       <c r="AX55" s="7"/>
     </row>
-    <row r="56" ht="20.25" hidden="1" customHeight="1">
+    <row r="56" ht="20.25" customHeight="1">
       <c r="A56" s="8">
         <v>826.0</v>
       </c>
@@ -12104,7 +12103,7 @@
       <c r="AW56" s="7"/>
       <c r="AX56" s="7"/>
     </row>
-    <row r="57" ht="20.25" hidden="1" customHeight="1">
+    <row r="57" ht="20.25" customHeight="1">
       <c r="A57" s="12">
         <v>827.0</v>
       </c>
@@ -12208,7 +12207,7 @@
       <c r="AW57" s="7"/>
       <c r="AX57" s="7"/>
     </row>
-    <row r="58" ht="20.25" hidden="1" customHeight="1">
+    <row r="58" ht="20.25" customHeight="1">
       <c r="A58" s="8">
         <v>828.0</v>
       </c>
@@ -12312,7 +12311,7 @@
       <c r="AW58" s="7"/>
       <c r="AX58" s="7"/>
     </row>
-    <row r="59" ht="20.25" hidden="1" customHeight="1">
+    <row r="59" ht="20.25" customHeight="1">
       <c r="A59" s="12">
         <v>829.0</v>
       </c>
@@ -12416,7 +12415,7 @@
       <c r="AW59" s="7"/>
       <c r="AX59" s="7"/>
     </row>
-    <row r="60" ht="20.25" hidden="1" customHeight="1">
+    <row r="60" ht="20.25" customHeight="1">
       <c r="A60" s="8">
         <v>830.0</v>
       </c>
@@ -12520,7 +12519,7 @@
       <c r="AW60" s="7"/>
       <c r="AX60" s="7"/>
     </row>
-    <row r="61" ht="20.25" hidden="1" customHeight="1">
+    <row r="61" ht="20.25" customHeight="1">
       <c r="A61" s="12">
         <v>831.0</v>
       </c>
@@ -12624,7 +12623,7 @@
       <c r="AW61" s="7"/>
       <c r="AX61" s="7"/>
     </row>
-    <row r="62" ht="20.25" hidden="1" customHeight="1">
+    <row r="62" ht="20.25" customHeight="1">
       <c r="A62" s="8">
         <v>832.0</v>
       </c>
@@ -12728,7 +12727,7 @@
       <c r="AW62" s="7"/>
       <c r="AX62" s="7"/>
     </row>
-    <row r="63" ht="20.25" hidden="1" customHeight="1">
+    <row r="63" ht="20.25" customHeight="1">
       <c r="A63" s="12">
         <v>833.0</v>
       </c>
@@ -12832,7 +12831,7 @@
       <c r="AW63" s="7"/>
       <c r="AX63" s="7"/>
     </row>
-    <row r="64" ht="20.25" hidden="1" customHeight="1">
+    <row r="64" ht="20.25" customHeight="1">
       <c r="A64" s="8">
         <v>834.0</v>
       </c>
@@ -12936,7 +12935,7 @@
       <c r="AW64" s="7"/>
       <c r="AX64" s="7"/>
     </row>
-    <row r="65" ht="20.25" hidden="1" customHeight="1">
+    <row r="65" ht="20.25" customHeight="1">
       <c r="A65" s="12">
         <v>835.0</v>
       </c>
@@ -13040,7 +13039,7 @@
       <c r="AW65" s="7"/>
       <c r="AX65" s="7"/>
     </row>
-    <row r="66" ht="20.25" hidden="1" customHeight="1">
+    <row r="66" ht="20.25" customHeight="1">
       <c r="A66" s="8">
         <v>836.0</v>
       </c>
@@ -13144,7 +13143,7 @@
       <c r="AW66" s="7"/>
       <c r="AX66" s="7"/>
     </row>
-    <row r="67" ht="20.25" hidden="1" customHeight="1">
+    <row r="67" ht="20.25" customHeight="1">
       <c r="A67" s="12">
         <v>837.0</v>
       </c>
@@ -13248,7 +13247,7 @@
       <c r="AW67" s="7"/>
       <c r="AX67" s="7"/>
     </row>
-    <row r="68" ht="20.25" hidden="1" customHeight="1">
+    <row r="68" ht="20.25" customHeight="1">
       <c r="A68" s="8">
         <v>838.0</v>
       </c>
@@ -13352,7 +13351,7 @@
       <c r="AW68" s="7"/>
       <c r="AX68" s="7"/>
     </row>
-    <row r="69" ht="20.25" hidden="1" customHeight="1">
+    <row r="69" ht="20.25" customHeight="1">
       <c r="A69" s="12">
         <v>839.0</v>
       </c>
@@ -13456,7 +13455,7 @@
       <c r="AW69" s="7"/>
       <c r="AX69" s="7"/>
     </row>
-    <row r="70" ht="20.25" hidden="1" customHeight="1">
+    <row r="70" ht="20.25" customHeight="1">
       <c r="A70" s="8">
         <v>840.0</v>
       </c>
@@ -13560,7 +13559,7 @@
       <c r="AW70" s="7"/>
       <c r="AX70" s="7"/>
     </row>
-    <row r="71" ht="20.25" hidden="1" customHeight="1">
+    <row r="71" ht="20.25" customHeight="1">
       <c r="A71" s="12">
         <v>841.0</v>
       </c>
@@ -13664,7 +13663,7 @@
       <c r="AW71" s="7"/>
       <c r="AX71" s="7"/>
     </row>
-    <row r="72" ht="20.25" hidden="1" customHeight="1">
+    <row r="72" ht="20.25" customHeight="1">
       <c r="A72" s="8">
         <v>842.0</v>
       </c>
@@ -13768,7 +13767,7 @@
       <c r="AW72" s="7"/>
       <c r="AX72" s="7"/>
     </row>
-    <row r="73" ht="20.25" hidden="1" customHeight="1">
+    <row r="73" ht="20.25" customHeight="1">
       <c r="A73" s="12">
         <v>843.0</v>
       </c>
@@ -13872,7 +13871,7 @@
       <c r="AW73" s="7"/>
       <c r="AX73" s="7"/>
     </row>
-    <row r="74" ht="20.25" hidden="1" customHeight="1">
+    <row r="74" ht="20.25" customHeight="1">
       <c r="A74" s="8">
         <v>844.0</v>
       </c>
@@ -13976,7 +13975,7 @@
       <c r="AW74" s="7"/>
       <c r="AX74" s="7"/>
     </row>
-    <row r="75" ht="20.25" hidden="1" customHeight="1">
+    <row r="75" ht="20.25" customHeight="1">
       <c r="A75" s="12">
         <v>845.0</v>
       </c>
@@ -14080,7 +14079,7 @@
       <c r="AW75" s="7"/>
       <c r="AX75" s="7"/>
     </row>
-    <row r="76" ht="20.25" hidden="1" customHeight="1">
+    <row r="76" ht="20.25" customHeight="1">
       <c r="A76" s="8">
         <v>846.0</v>
       </c>
@@ -14184,7 +14183,7 @@
       <c r="AW76" s="7"/>
       <c r="AX76" s="7"/>
     </row>
-    <row r="77" ht="20.25" hidden="1" customHeight="1">
+    <row r="77" ht="20.25" customHeight="1">
       <c r="A77" s="12">
         <v>847.0</v>
       </c>
@@ -14288,7 +14287,7 @@
       <c r="AW77" s="7"/>
       <c r="AX77" s="7"/>
     </row>
-    <row r="78" ht="20.25" hidden="1" customHeight="1">
+    <row r="78" ht="20.25" customHeight="1">
       <c r="A78" s="8">
         <v>848.0</v>
       </c>
@@ -14392,7 +14391,7 @@
       <c r="AW78" s="7"/>
       <c r="AX78" s="7"/>
     </row>
-    <row r="79" ht="20.25" hidden="1" customHeight="1">
+    <row r="79" ht="20.25" customHeight="1">
       <c r="A79" s="12">
         <v>849.0</v>
       </c>
@@ -14496,7 +14495,7 @@
       <c r="AW79" s="7"/>
       <c r="AX79" s="7"/>
     </row>
-    <row r="80" ht="20.25" hidden="1" customHeight="1">
+    <row r="80" ht="20.25" customHeight="1">
       <c r="A80" s="8">
         <v>850.0</v>
       </c>
@@ -14600,7 +14599,7 @@
       <c r="AW80" s="7"/>
       <c r="AX80" s="7"/>
     </row>
-    <row r="81" ht="20.25" hidden="1" customHeight="1">
+    <row r="81" ht="20.25" customHeight="1">
       <c r="A81" s="12">
         <v>851.0</v>
       </c>
@@ -14704,7 +14703,7 @@
       <c r="AW81" s="7"/>
       <c r="AX81" s="7"/>
     </row>
-    <row r="82" ht="20.25" hidden="1" customHeight="1">
+    <row r="82" ht="20.25" customHeight="1">
       <c r="A82" s="8">
         <v>852.0</v>
       </c>
@@ -14808,7 +14807,7 @@
       <c r="AW82" s="7"/>
       <c r="AX82" s="7"/>
     </row>
-    <row r="83" ht="20.25" hidden="1" customHeight="1">
+    <row r="83" ht="20.25" customHeight="1">
       <c r="A83" s="12">
         <v>853.0</v>
       </c>
@@ -14912,7 +14911,7 @@
       <c r="AW83" s="7"/>
       <c r="AX83" s="7"/>
     </row>
-    <row r="84" ht="20.25" hidden="1" customHeight="1">
+    <row r="84" ht="20.25" customHeight="1">
       <c r="A84" s="8">
         <v>854.0</v>
       </c>
@@ -15016,7 +15015,7 @@
       <c r="AW84" s="7"/>
       <c r="AX84" s="7"/>
     </row>
-    <row r="85" ht="20.25" hidden="1" customHeight="1">
+    <row r="85" ht="20.25" customHeight="1">
       <c r="A85" s="12">
         <v>855.0</v>
       </c>
@@ -15120,7 +15119,7 @@
       <c r="AW85" s="7"/>
       <c r="AX85" s="7"/>
     </row>
-    <row r="86" ht="20.25" hidden="1" customHeight="1">
+    <row r="86" ht="20.25" customHeight="1">
       <c r="A86" s="8">
         <v>856.0</v>
       </c>
@@ -15224,7 +15223,7 @@
       <c r="AW86" s="7"/>
       <c r="AX86" s="7"/>
     </row>
-    <row r="87" ht="20.25" hidden="1" customHeight="1">
+    <row r="87" ht="20.25" customHeight="1">
       <c r="A87" s="12">
         <v>857.0</v>
       </c>
@@ -15328,7 +15327,7 @@
       <c r="AW87" s="7"/>
       <c r="AX87" s="7"/>
     </row>
-    <row r="88" ht="20.25" hidden="1" customHeight="1">
+    <row r="88" ht="20.25" customHeight="1">
       <c r="A88" s="8">
         <v>858.0</v>
       </c>
@@ -15432,7 +15431,7 @@
       <c r="AW88" s="7"/>
       <c r="AX88" s="7"/>
     </row>
-    <row r="89" ht="20.25" hidden="1" customHeight="1">
+    <row r="89" ht="20.25" customHeight="1">
       <c r="A89" s="12">
         <v>859.0</v>
       </c>
@@ -15536,7 +15535,7 @@
       <c r="AW89" s="7"/>
       <c r="AX89" s="7"/>
     </row>
-    <row r="90" ht="20.25" hidden="1" customHeight="1">
+    <row r="90" ht="20.25" customHeight="1">
       <c r="A90" s="8">
         <v>860.0</v>
       </c>
@@ -15640,7 +15639,7 @@
       <c r="AW90" s="7"/>
       <c r="AX90" s="7"/>
     </row>
-    <row r="91" ht="20.25" hidden="1" customHeight="1">
+    <row r="91" ht="20.25" customHeight="1">
       <c r="A91" s="12">
         <v>861.0</v>
       </c>
@@ -15744,7 +15743,7 @@
       <c r="AW91" s="7"/>
       <c r="AX91" s="7"/>
     </row>
-    <row r="92" ht="20.25" hidden="1" customHeight="1">
+    <row r="92" ht="20.25" customHeight="1">
       <c r="A92" s="8">
         <v>862.0</v>
       </c>
@@ -15848,7 +15847,7 @@
       <c r="AW92" s="7"/>
       <c r="AX92" s="7"/>
     </row>
-    <row r="93" ht="20.25" hidden="1" customHeight="1">
+    <row r="93" ht="20.25" customHeight="1">
       <c r="A93" s="12">
         <v>863.0</v>
       </c>
@@ -15952,7 +15951,7 @@
       <c r="AW93" s="7"/>
       <c r="AX93" s="7"/>
     </row>
-    <row r="94" ht="20.25" hidden="1" customHeight="1">
+    <row r="94" ht="20.25" customHeight="1">
       <c r="A94" s="8">
         <v>864.0</v>
       </c>
@@ -16056,7 +16055,7 @@
       <c r="AW94" s="7"/>
       <c r="AX94" s="7"/>
     </row>
-    <row r="95" ht="20.25" hidden="1" customHeight="1">
+    <row r="95" ht="20.25" customHeight="1">
       <c r="A95" s="12">
         <v>865.0</v>
       </c>
@@ -16160,7 +16159,7 @@
       <c r="AW95" s="7"/>
       <c r="AX95" s="7"/>
     </row>
-    <row r="96" ht="20.25" hidden="1" customHeight="1">
+    <row r="96" ht="20.25" customHeight="1">
       <c r="A96" s="8">
         <v>866.0</v>
       </c>
@@ -16264,7 +16263,7 @@
       <c r="AW96" s="7"/>
       <c r="AX96" s="7"/>
     </row>
-    <row r="97" ht="20.25" hidden="1" customHeight="1">
+    <row r="97" ht="20.25" customHeight="1">
       <c r="A97" s="12">
         <v>867.0</v>
       </c>
@@ -16368,7 +16367,7 @@
       <c r="AW97" s="7"/>
       <c r="AX97" s="7"/>
     </row>
-    <row r="98" ht="20.25" hidden="1" customHeight="1">
+    <row r="98" ht="20.25" customHeight="1">
       <c r="A98" s="8">
         <v>868.0</v>
       </c>
@@ -16472,7 +16471,7 @@
       <c r="AW98" s="7"/>
       <c r="AX98" s="7"/>
     </row>
-    <row r="99" ht="20.25" hidden="1" customHeight="1">
+    <row r="99" ht="20.25" customHeight="1">
       <c r="A99" s="12">
         <v>869.0</v>
       </c>
@@ -16576,7 +16575,7 @@
       <c r="AW99" s="7"/>
       <c r="AX99" s="7"/>
     </row>
-    <row r="100" ht="20.25" hidden="1" customHeight="1">
+    <row r="100" ht="20.25" customHeight="1">
       <c r="A100" s="8">
         <v>870.0</v>
       </c>
@@ -16680,7 +16679,7 @@
       <c r="AW100" s="7"/>
       <c r="AX100" s="7"/>
     </row>
-    <row r="101" ht="20.25" hidden="1" customHeight="1">
+    <row r="101" ht="20.25" customHeight="1">
       <c r="A101" s="12">
         <v>871.0</v>
       </c>
@@ -16784,7 +16783,7 @@
       <c r="AW101" s="7"/>
       <c r="AX101" s="7"/>
     </row>
-    <row r="102" ht="20.25" hidden="1" customHeight="1">
+    <row r="102" ht="20.25" customHeight="1">
       <c r="A102" s="8">
         <v>872.0</v>
       </c>
@@ -16888,7 +16887,7 @@
       <c r="AW102" s="7"/>
       <c r="AX102" s="7"/>
     </row>
-    <row r="103" ht="20.25" hidden="1" customHeight="1">
+    <row r="103" ht="20.25" customHeight="1">
       <c r="A103" s="12">
         <v>873.0</v>
       </c>
@@ -16992,7 +16991,7 @@
       <c r="AW103" s="7"/>
       <c r="AX103" s="7"/>
     </row>
-    <row r="104" ht="20.25" hidden="1" customHeight="1">
+    <row r="104" ht="20.25" customHeight="1">
       <c r="A104" s="8">
         <v>43.0</v>
       </c>
@@ -17100,7 +17099,7 @@
       <c r="AW104" s="7"/>
       <c r="AX104" s="7"/>
     </row>
-    <row r="105" ht="20.25" hidden="1" customHeight="1">
+    <row r="105" ht="20.25" customHeight="1">
       <c r="A105" s="12">
         <v>44.0</v>
       </c>
@@ -17208,7 +17207,7 @@
       <c r="AW105" s="7"/>
       <c r="AX105" s="7"/>
     </row>
-    <row r="106" ht="20.25" hidden="1" customHeight="1">
+    <row r="106" ht="20.25" customHeight="1">
       <c r="A106" s="8">
         <v>58.0</v>
       </c>
@@ -17316,7 +17315,7 @@
       <c r="AW106" s="7"/>
       <c r="AX106" s="7"/>
     </row>
-    <row r="107" ht="20.25" hidden="1" customHeight="1">
+    <row r="107" ht="20.25" customHeight="1">
       <c r="A107" s="12">
         <v>1175.0</v>
       </c>
@@ -20244,7 +20243,7 @@
       <c r="AW133" s="7"/>
       <c r="AX133" s="7"/>
     </row>
-    <row r="134" ht="20.25" hidden="1" customHeight="1">
+    <row r="134" ht="20.25" customHeight="1">
       <c r="A134" s="8">
         <v>1204.0</v>
       </c>
@@ -20354,7 +20353,7 @@
       <c r="AW134" s="7"/>
       <c r="AX134" s="7"/>
     </row>
-    <row r="135" ht="20.25" hidden="1" customHeight="1">
+    <row r="135" ht="20.25" customHeight="1">
       <c r="A135" s="12">
         <v>1206.0</v>
       </c>
@@ -20464,7 +20463,7 @@
       <c r="AW135" s="7"/>
       <c r="AX135" s="7"/>
     </row>
-    <row r="136" ht="20.25" hidden="1" customHeight="1">
+    <row r="136" ht="20.25" customHeight="1">
       <c r="A136" s="8">
         <v>1207.0</v>
       </c>
@@ -20572,7 +20571,7 @@
       <c r="AW136" s="7"/>
       <c r="AX136" s="7"/>
     </row>
-    <row r="137" ht="20.25" hidden="1" customHeight="1">
+    <row r="137" ht="20.25" customHeight="1">
       <c r="A137" s="12">
         <v>1208.0</v>
       </c>
@@ -20680,7 +20679,7 @@
       <c r="AW137" s="7"/>
       <c r="AX137" s="7"/>
     </row>
-    <row r="138" ht="20.25" hidden="1" customHeight="1">
+    <row r="138" ht="20.25" customHeight="1">
       <c r="A138" s="8">
         <v>1209.0</v>
       </c>
@@ -20788,7 +20787,7 @@
       <c r="AW138" s="7"/>
       <c r="AX138" s="7"/>
     </row>
-    <row r="139" ht="20.25" hidden="1" customHeight="1">
+    <row r="139" ht="20.25" customHeight="1">
       <c r="A139" s="12">
         <v>1210.0</v>
       </c>
@@ -20896,7 +20895,7 @@
       <c r="AW139" s="7"/>
       <c r="AX139" s="7"/>
     </row>
-    <row r="140" ht="20.25" hidden="1" customHeight="1">
+    <row r="140" ht="20.25" customHeight="1">
       <c r="A140" s="8">
         <v>1211.0</v>
       </c>
@@ -21004,7 +21003,7 @@
       <c r="AW140" s="7"/>
       <c r="AX140" s="7"/>
     </row>
-    <row r="141" ht="20.25" hidden="1" customHeight="1">
+    <row r="141" ht="20.25" customHeight="1">
       <c r="A141" s="12">
         <v>1212.0</v>
       </c>
@@ -21112,7 +21111,7 @@
       <c r="AW141" s="7"/>
       <c r="AX141" s="7"/>
     </row>
-    <row r="142" ht="20.25" hidden="1" customHeight="1">
+    <row r="142" ht="20.25" customHeight="1">
       <c r="A142" s="8">
         <v>1213.0</v>
       </c>
@@ -21220,7 +21219,7 @@
       <c r="AW142" s="7"/>
       <c r="AX142" s="7"/>
     </row>
-    <row r="143" ht="20.25" hidden="1" customHeight="1">
+    <row r="143" ht="20.25" customHeight="1">
       <c r="A143" s="12">
         <v>1214.0</v>
       </c>
@@ -21328,7 +21327,7 @@
       <c r="AW143" s="7"/>
       <c r="AX143" s="7"/>
     </row>
-    <row r="144" ht="20.25" hidden="1" customHeight="1">
+    <row r="144" ht="20.25" customHeight="1">
       <c r="A144" s="8">
         <v>1215.0</v>
       </c>
@@ -21436,7 +21435,7 @@
       <c r="AW144" s="7"/>
       <c r="AX144" s="7"/>
     </row>
-    <row r="145" ht="20.25" hidden="1" customHeight="1">
+    <row r="145" ht="20.25" customHeight="1">
       <c r="A145" s="12">
         <v>1216.0</v>
       </c>
@@ -21544,7 +21543,7 @@
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
-    <row r="146" ht="20.25" hidden="1" customHeight="1">
+    <row r="146" ht="20.25" customHeight="1">
       <c r="A146" s="8">
         <v>1217.0</v>
       </c>
@@ -21652,7 +21651,7 @@
       <c r="AW146" s="7"/>
       <c r="AX146" s="7"/>
     </row>
-    <row r="147" ht="20.25" hidden="1" customHeight="1">
+    <row r="147" ht="20.25" customHeight="1">
       <c r="A147" s="12">
         <v>1218.0</v>
       </c>
@@ -21760,7 +21759,7 @@
       <c r="AW147" s="7"/>
       <c r="AX147" s="7"/>
     </row>
-    <row r="148" ht="20.25" hidden="1" customHeight="1">
+    <row r="148" ht="20.25" customHeight="1">
       <c r="A148" s="8">
         <v>1219.0</v>
       </c>
@@ -21868,7 +21867,7 @@
       <c r="AW148" s="7"/>
       <c r="AX148" s="7"/>
     </row>
-    <row r="149" ht="20.25" hidden="1" customHeight="1">
+    <row r="149" ht="20.25" customHeight="1">
       <c r="A149" s="12">
         <v>1220.0</v>
       </c>
@@ -21976,7 +21975,7 @@
       <c r="AW149" s="7"/>
       <c r="AX149" s="7"/>
     </row>
-    <row r="150" ht="20.25" hidden="1" customHeight="1">
+    <row r="150" ht="20.25" customHeight="1">
       <c r="A150" s="8">
         <v>1221.0</v>
       </c>
@@ -22084,7 +22083,7 @@
       <c r="AW150" s="7"/>
       <c r="AX150" s="7"/>
     </row>
-    <row r="151" ht="20.25" hidden="1" customHeight="1">
+    <row r="151" ht="20.25" customHeight="1">
       <c r="A151" s="12">
         <v>1222.0</v>
       </c>
@@ -22192,7 +22191,7 @@
       <c r="AW151" s="7"/>
       <c r="AX151" s="7"/>
     </row>
-    <row r="152" ht="20.25" hidden="1" customHeight="1">
+    <row r="152" ht="20.25" customHeight="1">
       <c r="A152" s="8">
         <v>1223.0</v>
       </c>
@@ -22300,7 +22299,7 @@
       <c r="AW152" s="7"/>
       <c r="AX152" s="7"/>
     </row>
-    <row r="153" ht="20.25" hidden="1" customHeight="1">
+    <row r="153" ht="20.25" customHeight="1">
       <c r="A153" s="12">
         <v>1224.0</v>
       </c>
@@ -22408,7 +22407,7 @@
       <c r="AW153" s="7"/>
       <c r="AX153" s="7"/>
     </row>
-    <row r="154" ht="20.25" hidden="1" customHeight="1">
+    <row r="154" ht="20.25" customHeight="1">
       <c r="A154" s="8">
         <v>1225.0</v>
       </c>
@@ -22516,7 +22515,7 @@
       <c r="AW154" s="7"/>
       <c r="AX154" s="7"/>
     </row>
-    <row r="155" ht="20.25" hidden="1" customHeight="1">
+    <row r="155" ht="20.25" customHeight="1">
       <c r="A155" s="12">
         <v>1226.0</v>
       </c>
@@ -22624,7 +22623,7 @@
       <c r="AW155" s="7"/>
       <c r="AX155" s="7"/>
     </row>
-    <row r="156" ht="20.25" hidden="1" customHeight="1">
+    <row r="156" ht="20.25" customHeight="1">
       <c r="A156" s="8">
         <v>1227.0</v>
       </c>
@@ -22732,7 +22731,7 @@
       <c r="AW156" s="7"/>
       <c r="AX156" s="7"/>
     </row>
-    <row r="157" ht="20.25" hidden="1" customHeight="1">
+    <row r="157" ht="20.25" customHeight="1">
       <c r="A157" s="12">
         <v>1228.0</v>
       </c>
@@ -22840,7 +22839,7 @@
       <c r="AW157" s="7"/>
       <c r="AX157" s="7"/>
     </row>
-    <row r="158" ht="20.25" hidden="1" customHeight="1">
+    <row r="158" ht="20.25" customHeight="1">
       <c r="A158" s="8">
         <v>1229.0</v>
       </c>
@@ -22948,7 +22947,7 @@
       <c r="AW158" s="7"/>
       <c r="AX158" s="7"/>
     </row>
-    <row r="159" ht="20.25" hidden="1" customHeight="1">
+    <row r="159" ht="20.25" customHeight="1">
       <c r="A159" s="12">
         <v>1230.0</v>
       </c>
@@ -23056,7 +23055,7 @@
       <c r="AW159" s="7"/>
       <c r="AX159" s="7"/>
     </row>
-    <row r="160" ht="20.25" hidden="1" customHeight="1">
+    <row r="160" ht="20.25" customHeight="1">
       <c r="A160" s="8">
         <v>1231.0</v>
       </c>
@@ -23164,7 +23163,7 @@
       <c r="AW160" s="7"/>
       <c r="AX160" s="7"/>
     </row>
-    <row r="161" ht="20.25" hidden="1" customHeight="1">
+    <row r="161" ht="20.25" customHeight="1">
       <c r="A161" s="12">
         <v>1232.0</v>
       </c>
@@ -23272,7 +23271,7 @@
       <c r="AW161" s="7"/>
       <c r="AX161" s="7"/>
     </row>
-    <row r="162" ht="20.25" hidden="1" customHeight="1">
+    <row r="162" ht="20.25" customHeight="1">
       <c r="A162" s="8">
         <v>1233.0</v>
       </c>
@@ -23380,7 +23379,7 @@
       <c r="AW162" s="7"/>
       <c r="AX162" s="7"/>
     </row>
-    <row r="163" ht="20.25" hidden="1" customHeight="1">
+    <row r="163" ht="20.25" customHeight="1">
       <c r="A163" s="12">
         <v>1234.0</v>
       </c>
@@ -23488,7 +23487,7 @@
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
-    <row r="164" ht="20.25" hidden="1" customHeight="1">
+    <row r="164" ht="20.25" customHeight="1">
       <c r="A164" s="8">
         <v>1235.0</v>
       </c>
@@ -23596,7 +23595,7 @@
       <c r="AW164" s="7"/>
       <c r="AX164" s="7"/>
     </row>
-    <row r="165" ht="20.25" hidden="1" customHeight="1">
+    <row r="165" ht="20.25" customHeight="1">
       <c r="A165" s="12">
         <v>1236.0</v>
       </c>
@@ -23704,7 +23703,7 @@
       <c r="AW165" s="7"/>
       <c r="AX165" s="7"/>
     </row>
-    <row r="166" ht="20.25" hidden="1" customHeight="1">
+    <row r="166" ht="20.25" customHeight="1">
       <c r="A166" s="8">
         <v>1237.0</v>
       </c>
@@ -23812,7 +23811,7 @@
       <c r="AW166" s="7"/>
       <c r="AX166" s="7"/>
     </row>
-    <row r="167" ht="20.25" hidden="1" customHeight="1">
+    <row r="167" ht="20.25" customHeight="1">
       <c r="A167" s="12">
         <v>1238.0</v>
       </c>
@@ -23920,7 +23919,7 @@
       <c r="AW167" s="7"/>
       <c r="AX167" s="7"/>
     </row>
-    <row r="168" ht="20.25" hidden="1" customHeight="1">
+    <row r="168" ht="20.25" customHeight="1">
       <c r="A168" s="8">
         <v>1239.0</v>
       </c>
@@ -24028,7 +24027,7 @@
       <c r="AW168" s="7"/>
       <c r="AX168" s="7"/>
     </row>
-    <row r="169" ht="20.25" hidden="1" customHeight="1">
+    <row r="169" ht="20.25" customHeight="1">
       <c r="A169" s="12">
         <v>1240.0</v>
       </c>
@@ -24136,7 +24135,7 @@
       <c r="AW169" s="7"/>
       <c r="AX169" s="7"/>
     </row>
-    <row r="170" ht="20.25" hidden="1" customHeight="1">
+    <row r="170" ht="20.25" customHeight="1">
       <c r="A170" s="8">
         <v>1241.0</v>
       </c>
@@ -24244,7 +24243,7 @@
       <c r="AW170" s="7"/>
       <c r="AX170" s="7"/>
     </row>
-    <row r="171" ht="20.25" hidden="1" customHeight="1">
+    <row r="171" ht="20.25" customHeight="1">
       <c r="A171" s="12">
         <v>1242.0</v>
       </c>
@@ -24352,7 +24351,7 @@
       <c r="AW171" s="7"/>
       <c r="AX171" s="7"/>
     </row>
-    <row r="172" ht="20.25" hidden="1" customHeight="1">
+    <row r="172" ht="20.25" customHeight="1">
       <c r="A172" s="8">
         <v>1243.0</v>
       </c>
@@ -24460,7 +24459,7 @@
       <c r="AW172" s="7"/>
       <c r="AX172" s="7"/>
     </row>
-    <row r="173" ht="20.25" hidden="1" customHeight="1">
+    <row r="173" ht="20.25" customHeight="1">
       <c r="A173" s="12">
         <v>1244.0</v>
       </c>
@@ -24568,7 +24567,7 @@
       <c r="AW173" s="7"/>
       <c r="AX173" s="7"/>
     </row>
-    <row r="174" ht="20.25" hidden="1" customHeight="1">
+    <row r="174" ht="20.25" customHeight="1">
       <c r="A174" s="8">
         <v>1245.0</v>
       </c>
@@ -24676,7 +24675,7 @@
       <c r="AW174" s="7"/>
       <c r="AX174" s="7"/>
     </row>
-    <row r="175" ht="20.25" hidden="1" customHeight="1">
+    <row r="175" ht="20.25" customHeight="1">
       <c r="A175" s="12">
         <v>1246.0</v>
       </c>
@@ -24784,7 +24783,7 @@
       <c r="AW175" s="7"/>
       <c r="AX175" s="7"/>
     </row>
-    <row r="176" ht="20.25" hidden="1" customHeight="1">
+    <row r="176" ht="20.25" customHeight="1">
       <c r="A176" s="8">
         <v>1247.0</v>
       </c>
@@ -24892,7 +24891,7 @@
       <c r="AW176" s="7"/>
       <c r="AX176" s="7"/>
     </row>
-    <row r="177" ht="20.25" hidden="1" customHeight="1">
+    <row r="177" ht="20.25" customHeight="1">
       <c r="A177" s="12">
         <v>1248.0</v>
       </c>
@@ -25000,7 +24999,7 @@
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
-    <row r="178" ht="20.25" hidden="1" customHeight="1">
+    <row r="178" ht="20.25" customHeight="1">
       <c r="A178" s="8">
         <v>1249.0</v>
       </c>
@@ -25108,7 +25107,7 @@
       <c r="AW178" s="7"/>
       <c r="AX178" s="7"/>
     </row>
-    <row r="179" ht="20.25" hidden="1" customHeight="1">
+    <row r="179" ht="20.25" customHeight="1">
       <c r="A179" s="12">
         <v>1250.0</v>
       </c>
@@ -25216,7 +25215,7 @@
       <c r="AW179" s="7"/>
       <c r="AX179" s="7"/>
     </row>
-    <row r="180" ht="20.25" hidden="1" customHeight="1">
+    <row r="180" ht="20.25" customHeight="1">
       <c r="A180" s="8">
         <v>1251.0</v>
       </c>
@@ -25324,7 +25323,7 @@
       <c r="AW180" s="7"/>
       <c r="AX180" s="7"/>
     </row>
-    <row r="181" ht="20.25" hidden="1" customHeight="1">
+    <row r="181" ht="20.25" customHeight="1">
       <c r="A181" s="12">
         <v>1252.0</v>
       </c>
@@ -25432,7 +25431,7 @@
       <c r="AW181" s="7"/>
       <c r="AX181" s="7"/>
     </row>
-    <row r="182" ht="20.25" hidden="1" customHeight="1">
+    <row r="182" ht="20.25" customHeight="1">
       <c r="A182" s="8">
         <v>1253.0</v>
       </c>
@@ -25540,7 +25539,7 @@
       <c r="AW182" s="7"/>
       <c r="AX182" s="7"/>
     </row>
-    <row r="183" ht="20.25" hidden="1" customHeight="1">
+    <row r="183" ht="20.25" customHeight="1">
       <c r="A183" s="12">
         <v>1254.0</v>
       </c>
@@ -25648,7 +25647,7 @@
       <c r="AW183" s="7"/>
       <c r="AX183" s="7"/>
     </row>
-    <row r="184" ht="20.25" hidden="1" customHeight="1">
+    <row r="184" ht="20.25" customHeight="1">
       <c r="A184" s="8">
         <v>1255.0</v>
       </c>
@@ -25758,7 +25757,7 @@
       <c r="AW184" s="7"/>
       <c r="AX184" s="7"/>
     </row>
-    <row r="185" ht="20.25" hidden="1" customHeight="1">
+    <row r="185" ht="20.25" customHeight="1">
       <c r="A185" s="12">
         <v>1256.0</v>
       </c>
@@ -25866,7 +25865,7 @@
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
-    <row r="186" ht="20.25" hidden="1" customHeight="1">
+    <row r="186" ht="20.25" customHeight="1">
       <c r="A186" s="8">
         <v>1257.0</v>
       </c>
@@ -25974,7 +25973,7 @@
       <c r="AW186" s="7"/>
       <c r="AX186" s="7"/>
     </row>
-    <row r="187" ht="20.25" hidden="1" customHeight="1">
+    <row r="187" ht="20.25" customHeight="1">
       <c r="A187" s="12">
         <v>1258.0</v>
       </c>
@@ -26082,7 +26081,7 @@
       <c r="AW187" s="7"/>
       <c r="AX187" s="7"/>
     </row>
-    <row r="188" ht="20.25" hidden="1" customHeight="1">
+    <row r="188" ht="20.25" customHeight="1">
       <c r="A188" s="8">
         <v>1259.0</v>
       </c>
@@ -26190,7 +26189,7 @@
       <c r="AW188" s="7"/>
       <c r="AX188" s="7"/>
     </row>
-    <row r="189" ht="20.25" hidden="1" customHeight="1">
+    <row r="189" ht="20.25" customHeight="1">
       <c r="A189" s="12">
         <v>1260.0</v>
       </c>
@@ -26298,7 +26297,7 @@
       <c r="AW189" s="7"/>
       <c r="AX189" s="7"/>
     </row>
-    <row r="190" ht="20.25" hidden="1" customHeight="1">
+    <row r="190" ht="20.25" customHeight="1">
       <c r="A190" s="8">
         <v>1261.0</v>
       </c>
@@ -26406,7 +26405,7 @@
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
-    <row r="191" ht="20.25" hidden="1" customHeight="1">
+    <row r="191" ht="20.25" customHeight="1">
       <c r="A191" s="12">
         <v>1262.0</v>
       </c>
@@ -26514,7 +26513,7 @@
       <c r="AW191" s="7"/>
       <c r="AX191" s="7"/>
     </row>
-    <row r="192" ht="20.25" hidden="1" customHeight="1">
+    <row r="192" ht="20.25" customHeight="1">
       <c r="A192" s="8">
         <v>1263.0</v>
       </c>
@@ -26622,7 +26621,7 @@
       <c r="AW192" s="7"/>
       <c r="AX192" s="7"/>
     </row>
-    <row r="193" ht="20.25" hidden="1" customHeight="1">
+    <row r="193" ht="20.25" customHeight="1">
       <c r="A193" s="12">
         <v>1264.0</v>
       </c>
@@ -26730,7 +26729,7 @@
       <c r="AW193" s="7"/>
       <c r="AX193" s="7"/>
     </row>
-    <row r="194" ht="20.25" hidden="1" customHeight="1">
+    <row r="194" ht="20.25" customHeight="1">
       <c r="A194" s="8">
         <v>1265.0</v>
       </c>
@@ -26838,7 +26837,7 @@
       <c r="AW194" s="7"/>
       <c r="AX194" s="7"/>
     </row>
-    <row r="195" ht="20.25" hidden="1" customHeight="1">
+    <row r="195" ht="20.25" customHeight="1">
       <c r="A195" s="12">
         <v>1266.0</v>
       </c>
@@ -26946,7 +26945,7 @@
       <c r="AW195" s="7"/>
       <c r="AX195" s="7"/>
     </row>
-    <row r="196" ht="20.25" hidden="1" customHeight="1">
+    <row r="196" ht="20.25" customHeight="1">
       <c r="A196" s="8">
         <v>1267.0</v>
       </c>
@@ -27054,7 +27053,7 @@
       <c r="AW196" s="7"/>
       <c r="AX196" s="7"/>
     </row>
-    <row r="197" ht="20.25" hidden="1" customHeight="1">
+    <row r="197" ht="20.25" customHeight="1">
       <c r="A197" s="12">
         <v>1269.0</v>
       </c>
@@ -27164,7 +27163,7 @@
       <c r="AW197" s="7"/>
       <c r="AX197" s="7"/>
     </row>
-    <row r="198" ht="20.25" hidden="1" customHeight="1">
+    <row r="198" ht="20.25" customHeight="1">
       <c r="A198" s="8">
         <v>1270.0</v>
       </c>
@@ -27274,7 +27273,7 @@
       <c r="AW198" s="7"/>
       <c r="AX198" s="7"/>
     </row>
-    <row r="199" ht="20.25" hidden="1" customHeight="1">
+    <row r="199" ht="20.25" customHeight="1">
       <c r="A199" s="12">
         <v>1271.0</v>
       </c>
@@ -27384,7 +27383,7 @@
       <c r="AW199" s="7"/>
       <c r="AX199" s="7"/>
     </row>
-    <row r="200" ht="20.25" hidden="1" customHeight="1">
+    <row r="200" ht="20.25" customHeight="1">
       <c r="A200" s="8">
         <v>1272.0</v>
       </c>
@@ -27492,7 +27491,7 @@
       <c r="AW200" s="7"/>
       <c r="AX200" s="7"/>
     </row>
-    <row r="201" ht="20.25" hidden="1" customHeight="1">
+    <row r="201" ht="20.25" customHeight="1">
       <c r="A201" s="12">
         <v>1273.0</v>
       </c>
@@ -27600,7 +27599,7 @@
       <c r="AW201" s="7"/>
       <c r="AX201" s="7"/>
     </row>
-    <row r="202" ht="20.25" hidden="1" customHeight="1">
+    <row r="202" ht="20.25" customHeight="1">
       <c r="A202" s="8">
         <v>1274.0</v>
       </c>
@@ -27708,7 +27707,7 @@
       <c r="AW202" s="7"/>
       <c r="AX202" s="7"/>
     </row>
-    <row r="203" ht="20.25" hidden="1" customHeight="1">
+    <row r="203" ht="20.25" customHeight="1">
       <c r="A203" s="12">
         <v>1275.0</v>
       </c>
@@ -27816,7 +27815,7 @@
       <c r="AW203" s="7"/>
       <c r="AX203" s="7"/>
     </row>
-    <row r="204" ht="20.25" hidden="1" customHeight="1">
+    <row r="204" ht="20.25" customHeight="1">
       <c r="A204" s="8">
         <v>1276.0</v>
       </c>
@@ -27924,7 +27923,7 @@
       <c r="AW204" s="7"/>
       <c r="AX204" s="7"/>
     </row>
-    <row r="205" ht="20.25" hidden="1" customHeight="1">
+    <row r="205" ht="20.25" customHeight="1">
       <c r="A205" s="12">
         <v>1277.0</v>
       </c>
@@ -28032,7 +28031,7 @@
       <c r="AW205" s="7"/>
       <c r="AX205" s="7"/>
     </row>
-    <row r="206" ht="20.25" hidden="1" customHeight="1">
+    <row r="206" ht="20.25" customHeight="1">
       <c r="A206" s="8">
         <v>1278.0</v>
       </c>
@@ -28140,7 +28139,7 @@
       <c r="AW206" s="7"/>
       <c r="AX206" s="7"/>
     </row>
-    <row r="207" ht="20.25" hidden="1" customHeight="1">
+    <row r="207" ht="20.25" customHeight="1">
       <c r="A207" s="12">
         <v>1279.0</v>
       </c>
@@ -28248,7 +28247,7 @@
       <c r="AW207" s="7"/>
       <c r="AX207" s="7"/>
     </row>
-    <row r="208" ht="20.25" hidden="1" customHeight="1">
+    <row r="208" ht="20.25" customHeight="1">
       <c r="A208" s="8">
         <v>1280.0</v>
       </c>
@@ -28356,7 +28355,7 @@
       <c r="AW208" s="7"/>
       <c r="AX208" s="7"/>
     </row>
-    <row r="209" ht="20.25" hidden="1" customHeight="1">
+    <row r="209" ht="20.25" customHeight="1">
       <c r="A209" s="12">
         <v>1281.0</v>
       </c>
@@ -28464,7 +28463,7 @@
       <c r="AW209" s="7"/>
       <c r="AX209" s="7"/>
     </row>
-    <row r="210" ht="20.25" hidden="1" customHeight="1">
+    <row r="210" ht="20.25" customHeight="1">
       <c r="A210" s="8">
         <v>1282.0</v>
       </c>
@@ -28572,7 +28571,7 @@
       <c r="AW210" s="7"/>
       <c r="AX210" s="7"/>
     </row>
-    <row r="211" ht="20.25" hidden="1" customHeight="1">
+    <row r="211" ht="20.25" customHeight="1">
       <c r="A211" s="12">
         <v>1283.0</v>
       </c>
@@ -28680,7 +28679,7 @@
       <c r="AW211" s="7"/>
       <c r="AX211" s="7"/>
     </row>
-    <row r="212" ht="20.25" hidden="1" customHeight="1">
+    <row r="212" ht="20.25" customHeight="1">
       <c r="A212" s="8">
         <v>1284.0</v>
       </c>
@@ -28788,7 +28787,7 @@
       <c r="AW212" s="7"/>
       <c r="AX212" s="7"/>
     </row>
-    <row r="213" ht="20.25" hidden="1" customHeight="1">
+    <row r="213" ht="20.25" customHeight="1">
       <c r="A213" s="12">
         <v>1285.0</v>
       </c>
@@ -28896,7 +28895,7 @@
       <c r="AW213" s="7"/>
       <c r="AX213" s="7"/>
     </row>
-    <row r="214" ht="20.25" hidden="1" customHeight="1">
+    <row r="214" ht="20.25" customHeight="1">
       <c r="A214" s="8">
         <v>1286.0</v>
       </c>
@@ -29004,7 +29003,7 @@
       <c r="AW214" s="7"/>
       <c r="AX214" s="7"/>
     </row>
-    <row r="215" ht="20.25" hidden="1" customHeight="1">
+    <row r="215" ht="20.25" customHeight="1">
       <c r="A215" s="12">
         <v>1287.0</v>
       </c>
@@ -29112,7 +29111,7 @@
       <c r="AW215" s="7"/>
       <c r="AX215" s="7"/>
     </row>
-    <row r="216" ht="20.25" hidden="1" customHeight="1">
+    <row r="216" ht="20.25" customHeight="1">
       <c r="A216" s="8">
         <v>1288.0</v>
       </c>
@@ -29220,7 +29219,7 @@
       <c r="AW216" s="7"/>
       <c r="AX216" s="7"/>
     </row>
-    <row r="217" ht="20.25" hidden="1" customHeight="1">
+    <row r="217" ht="20.25" customHeight="1">
       <c r="A217" s="12">
         <v>1289.0</v>
       </c>
@@ -29328,7 +29327,7 @@
       <c r="AW217" s="7"/>
       <c r="AX217" s="7"/>
     </row>
-    <row r="218" ht="20.25" hidden="1" customHeight="1">
+    <row r="218" ht="20.25" customHeight="1">
       <c r="A218" s="8">
         <v>1290.0</v>
       </c>
@@ -29436,7 +29435,7 @@
       <c r="AW218" s="7"/>
       <c r="AX218" s="7"/>
     </row>
-    <row r="219" ht="20.25" hidden="1" customHeight="1">
+    <row r="219" ht="20.25" customHeight="1">
       <c r="A219" s="12">
         <v>1291.0</v>
       </c>
@@ -29544,7 +29543,7 @@
       <c r="AW219" s="7"/>
       <c r="AX219" s="7"/>
     </row>
-    <row r="220" ht="20.25" hidden="1" customHeight="1">
+    <row r="220" ht="20.25" customHeight="1">
       <c r="A220" s="8">
         <v>1292.0</v>
       </c>
@@ -29652,7 +29651,7 @@
       <c r="AW220" s="7"/>
       <c r="AX220" s="7"/>
     </row>
-    <row r="221" ht="20.25" hidden="1" customHeight="1">
+    <row r="221" ht="20.25" customHeight="1">
       <c r="A221" s="12">
         <v>1293.0</v>
       </c>
@@ -29760,7 +29759,7 @@
       <c r="AW221" s="7"/>
       <c r="AX221" s="7"/>
     </row>
-    <row r="222" ht="20.25" hidden="1" customHeight="1">
+    <row r="222" ht="20.25" customHeight="1">
       <c r="A222" s="8">
         <v>1294.0</v>
       </c>
@@ -29868,7 +29867,7 @@
       <c r="AW222" s="7"/>
       <c r="AX222" s="7"/>
     </row>
-    <row r="223" ht="20.25" hidden="1" customHeight="1">
+    <row r="223" ht="20.25" customHeight="1">
       <c r="A223" s="12">
         <v>1295.0</v>
       </c>
@@ -29976,7 +29975,7 @@
       <c r="AW223" s="7"/>
       <c r="AX223" s="7"/>
     </row>
-    <row r="224" ht="20.25" hidden="1" customHeight="1">
+    <row r="224" ht="20.25" customHeight="1">
       <c r="A224" s="8">
         <v>1296.0</v>
       </c>
@@ -30084,7 +30083,7 @@
       <c r="AW224" s="7"/>
       <c r="AX224" s="7"/>
     </row>
-    <row r="225" ht="20.25" hidden="1" customHeight="1">
+    <row r="225" ht="20.25" customHeight="1">
       <c r="A225" s="12">
         <v>1297.0</v>
       </c>
@@ -30192,7 +30191,7 @@
       <c r="AW225" s="7"/>
       <c r="AX225" s="7"/>
     </row>
-    <row r="226" ht="20.25" hidden="1" customHeight="1">
+    <row r="226" ht="20.25" customHeight="1">
       <c r="A226" s="8">
         <v>1298.0</v>
       </c>
@@ -30300,7 +30299,7 @@
       <c r="AW226" s="7"/>
       <c r="AX226" s="7"/>
     </row>
-    <row r="227" ht="20.25" hidden="1" customHeight="1">
+    <row r="227" ht="20.25" customHeight="1">
       <c r="A227" s="12">
         <v>1299.0</v>
       </c>
@@ -30408,7 +30407,7 @@
       <c r="AW227" s="7"/>
       <c r="AX227" s="7"/>
     </row>
-    <row r="228" ht="20.25" hidden="1" customHeight="1">
+    <row r="228" ht="20.25" customHeight="1">
       <c r="A228" s="8">
         <v>1300.0</v>
       </c>
@@ -30516,7 +30515,7 @@
       <c r="AW228" s="7"/>
       <c r="AX228" s="7"/>
     </row>
-    <row r="229" ht="20.25" hidden="1" customHeight="1">
+    <row r="229" ht="20.25" customHeight="1">
       <c r="A229" s="12">
         <v>1301.0</v>
       </c>
@@ -30626,7 +30625,7 @@
       <c r="AW229" s="7"/>
       <c r="AX229" s="7"/>
     </row>
-    <row r="230" ht="20.25" hidden="1" customHeight="1">
+    <row r="230" ht="20.25" customHeight="1">
       <c r="A230" s="8">
         <v>1302.0</v>
       </c>
@@ -30734,7 +30733,7 @@
       <c r="AW230" s="7"/>
       <c r="AX230" s="7"/>
     </row>
-    <row r="231" ht="20.25" hidden="1" customHeight="1">
+    <row r="231" ht="20.25" customHeight="1">
       <c r="A231" s="12">
         <v>1303.0</v>
       </c>
@@ -30842,7 +30841,7 @@
       <c r="AW231" s="7"/>
       <c r="AX231" s="7"/>
     </row>
-    <row r="232" ht="20.25" hidden="1" customHeight="1">
+    <row r="232" ht="20.25" customHeight="1">
       <c r="A232" s="8">
         <v>1304.0</v>
       </c>
@@ -30952,7 +30951,7 @@
       <c r="AW232" s="7"/>
       <c r="AX232" s="7"/>
     </row>
-    <row r="233" ht="20.25" hidden="1" customHeight="1">
+    <row r="233" ht="20.25" customHeight="1">
       <c r="A233" s="12">
         <v>1305.0</v>
       </c>
@@ -31060,7 +31059,7 @@
       <c r="AW233" s="7"/>
       <c r="AX233" s="7"/>
     </row>
-    <row r="234" ht="20.25" hidden="1" customHeight="1">
+    <row r="234" ht="20.25" customHeight="1">
       <c r="A234" s="8">
         <v>1306.0</v>
       </c>
@@ -31168,7 +31167,7 @@
       <c r="AW234" s="7"/>
       <c r="AX234" s="7"/>
     </row>
-    <row r="235" ht="20.25" hidden="1" customHeight="1">
+    <row r="235" ht="20.25" customHeight="1">
       <c r="A235" s="12">
         <v>1307.0</v>
       </c>
@@ -31276,7 +31275,7 @@
       <c r="AW235" s="7"/>
       <c r="AX235" s="7"/>
     </row>
-    <row r="236" ht="20.25" hidden="1" customHeight="1">
+    <row r="236" ht="20.25" customHeight="1">
       <c r="A236" s="8">
         <v>1308.0</v>
       </c>
@@ -31384,7 +31383,7 @@
       <c r="AW236" s="7"/>
       <c r="AX236" s="7"/>
     </row>
-    <row r="237" ht="20.25" hidden="1" customHeight="1">
+    <row r="237" ht="20.25" customHeight="1">
       <c r="A237" s="12">
         <v>1309.0</v>
       </c>
@@ -31492,7 +31491,7 @@
       <c r="AW237" s="7"/>
       <c r="AX237" s="7"/>
     </row>
-    <row r="238" ht="20.25" hidden="1" customHeight="1">
+    <row r="238" ht="20.25" customHeight="1">
       <c r="A238" s="8">
         <v>1310.0</v>
       </c>
@@ -31600,7 +31599,7 @@
       <c r="AW238" s="7"/>
       <c r="AX238" s="7"/>
     </row>
-    <row r="239" ht="20.25" hidden="1" customHeight="1">
+    <row r="239" ht="20.25" customHeight="1">
       <c r="A239" s="12">
         <v>1311.0</v>
       </c>
@@ -31708,7 +31707,7 @@
       <c r="AW239" s="7"/>
       <c r="AX239" s="7"/>
     </row>
-    <row r="240" ht="20.25" hidden="1" customHeight="1">
+    <row r="240" ht="20.25" customHeight="1">
       <c r="A240" s="8">
         <v>1312.0</v>
       </c>
@@ -31816,7 +31815,7 @@
       <c r="AW240" s="7"/>
       <c r="AX240" s="7"/>
     </row>
-    <row r="241" ht="20.25" hidden="1" customHeight="1">
+    <row r="241" ht="20.25" customHeight="1">
       <c r="A241" s="12">
         <v>1313.0</v>
       </c>
@@ -31924,7 +31923,7 @@
       <c r="AW241" s="7"/>
       <c r="AX241" s="7"/>
     </row>
-    <row r="242" ht="20.25" hidden="1" customHeight="1">
+    <row r="242" ht="20.25" customHeight="1">
       <c r="A242" s="8">
         <v>1314.0</v>
       </c>
@@ -32032,7 +32031,7 @@
       <c r="AW242" s="7"/>
       <c r="AX242" s="7"/>
     </row>
-    <row r="243" ht="20.25" hidden="1" customHeight="1">
+    <row r="243" ht="20.25" customHeight="1">
       <c r="A243" s="12">
         <v>1315.0</v>
       </c>
@@ -32140,7 +32139,7 @@
       <c r="AW243" s="7"/>
       <c r="AX243" s="7"/>
     </row>
-    <row r="244" ht="20.25" hidden="1" customHeight="1">
+    <row r="244" ht="20.25" customHeight="1">
       <c r="A244" s="8">
         <v>1316.0</v>
       </c>
@@ -32248,7 +32247,7 @@
       <c r="AW244" s="7"/>
       <c r="AX244" s="7"/>
     </row>
-    <row r="245" ht="20.25" hidden="1" customHeight="1">
+    <row r="245" ht="20.25" customHeight="1">
       <c r="A245" s="12">
         <v>1317.0</v>
       </c>
@@ -32358,7 +32357,7 @@
       <c r="AW245" s="7"/>
       <c r="AX245" s="7"/>
     </row>
-    <row r="246" ht="20.25" hidden="1" customHeight="1">
+    <row r="246" ht="20.25" customHeight="1">
       <c r="A246" s="8">
         <v>1318.0</v>
       </c>
@@ -32468,7 +32467,7 @@
       <c r="AW246" s="7"/>
       <c r="AX246" s="7"/>
     </row>
-    <row r="247" ht="20.25" hidden="1" customHeight="1">
+    <row r="247" ht="20.25" customHeight="1">
       <c r="A247" s="12">
         <v>1319.0</v>
       </c>
@@ -32578,7 +32577,7 @@
       <c r="AW247" s="7"/>
       <c r="AX247" s="7"/>
     </row>
-    <row r="248" ht="20.25" hidden="1" customHeight="1">
+    <row r="248" ht="20.25" customHeight="1">
       <c r="A248" s="8">
         <v>1321.0</v>
       </c>
@@ -32688,7 +32687,7 @@
       <c r="AW248" s="7"/>
       <c r="AX248" s="7"/>
     </row>
-    <row r="249" ht="20.25" hidden="1" customHeight="1">
+    <row r="249" ht="20.25" customHeight="1">
       <c r="A249" s="12">
         <v>1323.0</v>
       </c>
@@ -32798,7 +32797,7 @@
       <c r="AW249" s="7"/>
       <c r="AX249" s="7"/>
     </row>
-    <row r="250" ht="20.25" hidden="1" customHeight="1">
+    <row r="250" ht="20.25" customHeight="1">
       <c r="A250" s="8">
         <v>1325.0</v>
       </c>
@@ -32908,7 +32907,7 @@
       <c r="AW250" s="7"/>
       <c r="AX250" s="7"/>
     </row>
-    <row r="251" ht="20.25" hidden="1" customHeight="1">
+    <row r="251" ht="20.25" customHeight="1">
       <c r="A251" s="12">
         <v>1327.0</v>
       </c>
@@ -33018,7 +33017,7 @@
       <c r="AW251" s="7"/>
       <c r="AX251" s="7"/>
     </row>
-    <row r="252" ht="20.25" hidden="1" customHeight="1">
+    <row r="252" ht="20.25" customHeight="1">
       <c r="A252" s="8">
         <v>1328.0</v>
       </c>
@@ -33128,7 +33127,7 @@
       <c r="AW252" s="7"/>
       <c r="AX252" s="7"/>
     </row>
-    <row r="253" ht="20.25" hidden="1" customHeight="1">
+    <row r="253" ht="20.25" customHeight="1">
       <c r="A253" s="12">
         <v>1329.0</v>
       </c>
@@ -33238,7 +33237,7 @@
       <c r="AW253" s="7"/>
       <c r="AX253" s="7"/>
     </row>
-    <row r="254" ht="20.25" hidden="1" customHeight="1">
+    <row r="254" ht="20.25" customHeight="1">
       <c r="A254" s="8">
         <v>1331.0</v>
       </c>
@@ -33348,7 +33347,7 @@
       <c r="AW254" s="7"/>
       <c r="AX254" s="7"/>
     </row>
-    <row r="255" ht="20.25" hidden="1" customHeight="1">
+    <row r="255" ht="20.25" customHeight="1">
       <c r="A255" s="12">
         <v>1332.0</v>
       </c>
@@ -33458,7 +33457,7 @@
       <c r="AW255" s="7"/>
       <c r="AX255" s="7"/>
     </row>
-    <row r="256" ht="20.25" hidden="1" customHeight="1">
+    <row r="256" ht="20.25" customHeight="1">
       <c r="A256" s="8">
         <v>1333.0</v>
       </c>
@@ -33568,7 +33567,7 @@
       <c r="AW256" s="7"/>
       <c r="AX256" s="7"/>
     </row>
-    <row r="257" ht="20.25" hidden="1" customHeight="1">
+    <row r="257" ht="20.25" customHeight="1">
       <c r="A257" s="12">
         <v>1334.0</v>
       </c>
@@ -33678,7 +33677,7 @@
       <c r="AW257" s="7"/>
       <c r="AX257" s="7"/>
     </row>
-    <row r="258" ht="20.25" hidden="1" customHeight="1">
+    <row r="258" ht="20.25" customHeight="1">
       <c r="A258" s="8">
         <v>1335.0</v>
       </c>
@@ -33786,7 +33785,7 @@
       <c r="AW258" s="7"/>
       <c r="AX258" s="7"/>
     </row>
-    <row r="259" ht="20.25" hidden="1" customHeight="1">
+    <row r="259" ht="20.25" customHeight="1">
       <c r="A259" s="12">
         <v>1336.0</v>
       </c>
@@ -33894,7 +33893,7 @@
       <c r="AW259" s="7"/>
       <c r="AX259" s="7"/>
     </row>
-    <row r="260" ht="20.25" hidden="1" customHeight="1">
+    <row r="260" ht="20.25" customHeight="1">
       <c r="A260" s="8">
         <v>1337.0</v>
       </c>
@@ -34002,7 +34001,7 @@
       <c r="AW260" s="7"/>
       <c r="AX260" s="7"/>
     </row>
-    <row r="261" ht="20.25" hidden="1" customHeight="1">
+    <row r="261" ht="20.25" customHeight="1">
       <c r="A261" s="12">
         <v>1338.0</v>
       </c>
@@ -34110,7 +34109,7 @@
       <c r="AW261" s="7"/>
       <c r="AX261" s="7"/>
     </row>
-    <row r="262" ht="20.25" hidden="1" customHeight="1">
+    <row r="262" ht="20.25" customHeight="1">
       <c r="A262" s="8">
         <v>1339.0</v>
       </c>
@@ -34218,7 +34217,7 @@
       <c r="AW262" s="7"/>
       <c r="AX262" s="7"/>
     </row>
-    <row r="263" ht="20.25" hidden="1" customHeight="1">
+    <row r="263" ht="20.25" customHeight="1">
       <c r="A263" s="12">
         <v>1340.0</v>
       </c>
@@ -34326,7 +34325,7 @@
       <c r="AW263" s="7"/>
       <c r="AX263" s="7"/>
     </row>
-    <row r="264" ht="20.25" hidden="1" customHeight="1">
+    <row r="264" ht="20.25" customHeight="1">
       <c r="A264" s="8">
         <v>1341.0</v>
       </c>
@@ -34434,7 +34433,7 @@
       <c r="AW264" s="7"/>
       <c r="AX264" s="7"/>
     </row>
-    <row r="265" ht="20.25" hidden="1" customHeight="1">
+    <row r="265" ht="20.25" customHeight="1">
       <c r="A265" s="12">
         <v>1342.0</v>
       </c>
@@ -34542,7 +34541,7 @@
       <c r="AW265" s="7"/>
       <c r="AX265" s="7"/>
     </row>
-    <row r="266" ht="20.25" hidden="1" customHeight="1">
+    <row r="266" ht="20.25" customHeight="1">
       <c r="A266" s="8">
         <v>1343.0</v>
       </c>
@@ -34650,7 +34649,7 @@
       <c r="AW266" s="7"/>
       <c r="AX266" s="7"/>
     </row>
-    <row r="267" ht="20.25" hidden="1" customHeight="1">
+    <row r="267" ht="20.25" customHeight="1">
       <c r="A267" s="12">
         <v>1344.0</v>
       </c>
@@ -34758,7 +34757,7 @@
       <c r="AW267" s="7"/>
       <c r="AX267" s="7"/>
     </row>
-    <row r="268" ht="20.25" hidden="1" customHeight="1">
+    <row r="268" ht="20.25" customHeight="1">
       <c r="A268" s="8">
         <v>1345.0</v>
       </c>
@@ -34866,7 +34865,7 @@
       <c r="AW268" s="7"/>
       <c r="AX268" s="7"/>
     </row>
-    <row r="269" ht="20.25" hidden="1" customHeight="1">
+    <row r="269" ht="20.25" customHeight="1">
       <c r="A269" s="12">
         <v>1346.0</v>
       </c>
@@ -34974,7 +34973,7 @@
       <c r="AW269" s="7"/>
       <c r="AX269" s="7"/>
     </row>
-    <row r="270" ht="20.25" hidden="1" customHeight="1">
+    <row r="270" ht="20.25" customHeight="1">
       <c r="A270" s="8">
         <v>1347.0</v>
       </c>
@@ -35082,7 +35081,7 @@
       <c r="AW270" s="7"/>
       <c r="AX270" s="7"/>
     </row>
-    <row r="271" ht="20.25" hidden="1" customHeight="1">
+    <row r="271" ht="20.25" customHeight="1">
       <c r="A271" s="12">
         <v>1348.0</v>
       </c>
@@ -35190,7 +35189,7 @@
       <c r="AW271" s="7"/>
       <c r="AX271" s="7"/>
     </row>
-    <row r="272" ht="20.25" hidden="1" customHeight="1">
+    <row r="272" ht="20.25" customHeight="1">
       <c r="A272" s="8">
         <v>1349.0</v>
       </c>
@@ -35298,7 +35297,7 @@
       <c r="AW272" s="7"/>
       <c r="AX272" s="7"/>
     </row>
-    <row r="273" ht="20.25" hidden="1" customHeight="1">
+    <row r="273" ht="20.25" customHeight="1">
       <c r="A273" s="12">
         <v>1350.0</v>
       </c>
@@ -35406,7 +35405,7 @@
       <c r="AW273" s="7"/>
       <c r="AX273" s="7"/>
     </row>
-    <row r="274" ht="20.25" hidden="1" customHeight="1">
+    <row r="274" ht="20.25" customHeight="1">
       <c r="A274" s="8">
         <v>1351.0</v>
       </c>
@@ -35514,7 +35513,7 @@
       <c r="AW274" s="7"/>
       <c r="AX274" s="7"/>
     </row>
-    <row r="275" ht="20.25" hidden="1" customHeight="1">
+    <row r="275" ht="20.25" customHeight="1">
       <c r="A275" s="12">
         <v>1352.0</v>
       </c>
@@ -35622,7 +35621,7 @@
       <c r="AW275" s="7"/>
       <c r="AX275" s="7"/>
     </row>
-    <row r="276" ht="20.25" hidden="1" customHeight="1">
+    <row r="276" ht="20.25" customHeight="1">
       <c r="A276" s="8">
         <v>1353.0</v>
       </c>
@@ -35730,7 +35729,7 @@
       <c r="AW276" s="7"/>
       <c r="AX276" s="7"/>
     </row>
-    <row r="277" ht="20.25" hidden="1" customHeight="1">
+    <row r="277" ht="20.25" customHeight="1">
       <c r="A277" s="12">
         <v>1354.0</v>
       </c>
@@ -35838,7 +35837,7 @@
       <c r="AW277" s="7"/>
       <c r="AX277" s="7"/>
     </row>
-    <row r="278" ht="20.25" hidden="1" customHeight="1">
+    <row r="278" ht="20.25" customHeight="1">
       <c r="A278" s="8">
         <v>1355.0</v>
       </c>
@@ -35946,7 +35945,7 @@
       <c r="AW278" s="7"/>
       <c r="AX278" s="7"/>
     </row>
-    <row r="279" ht="20.25" hidden="1" customHeight="1">
+    <row r="279" ht="20.25" customHeight="1">
       <c r="A279" s="12">
         <v>1356.0</v>
       </c>
@@ -36056,7 +36055,7 @@
       <c r="AW279" s="7"/>
       <c r="AX279" s="7"/>
     </row>
-    <row r="280" ht="20.25" hidden="1" customHeight="1">
+    <row r="280" ht="20.25" customHeight="1">
       <c r="A280" s="8">
         <v>1357.0</v>
       </c>
@@ -36166,7 +36165,7 @@
       <c r="AW280" s="7"/>
       <c r="AX280" s="7"/>
     </row>
-    <row r="281" ht="20.25" hidden="1" customHeight="1">
+    <row r="281" ht="20.25" customHeight="1">
       <c r="A281" s="12">
         <v>1359.0</v>
       </c>
@@ -36276,7 +36275,7 @@
       <c r="AW281" s="7"/>
       <c r="AX281" s="7"/>
     </row>
-    <row r="282" ht="20.25" hidden="1" customHeight="1">
+    <row r="282" ht="20.25" customHeight="1">
       <c r="A282" s="8">
         <v>1360.0</v>
       </c>
@@ -36384,7 +36383,7 @@
       <c r="AW282" s="7"/>
       <c r="AX282" s="7"/>
     </row>
-    <row r="283" ht="20.25" hidden="1" customHeight="1">
+    <row r="283" ht="20.25" customHeight="1">
       <c r="A283" s="12">
         <v>1361.0</v>
       </c>
@@ -36492,7 +36491,7 @@
       <c r="AW283" s="7"/>
       <c r="AX283" s="7"/>
     </row>
-    <row r="284" ht="20.25" hidden="1" customHeight="1">
+    <row r="284" ht="20.25" customHeight="1">
       <c r="A284" s="8">
         <v>1362.0</v>
       </c>
@@ -36600,7 +36599,7 @@
       <c r="AW284" s="7"/>
       <c r="AX284" s="7"/>
     </row>
-    <row r="285" ht="20.25" hidden="1" customHeight="1">
+    <row r="285" ht="20.25" customHeight="1">
       <c r="A285" s="12">
         <v>1363.0</v>
       </c>
@@ -36708,7 +36707,7 @@
       <c r="AW285" s="7"/>
       <c r="AX285" s="7"/>
     </row>
-    <row r="286" ht="20.25" hidden="1" customHeight="1">
+    <row r="286" ht="20.25" customHeight="1">
       <c r="A286" s="8">
         <v>1364.0</v>
       </c>
@@ -36816,7 +36815,7 @@
       <c r="AW286" s="7"/>
       <c r="AX286" s="7"/>
     </row>
-    <row r="287" ht="20.25" hidden="1" customHeight="1">
+    <row r="287" ht="20.25" customHeight="1">
       <c r="A287" s="12">
         <v>1365.0</v>
       </c>
@@ -36924,7 +36923,7 @@
       <c r="AW287" s="7"/>
       <c r="AX287" s="7"/>
     </row>
-    <row r="288" ht="20.25" hidden="1" customHeight="1">
+    <row r="288" ht="20.25" customHeight="1">
       <c r="A288" s="8">
         <v>1366.0</v>
       </c>
@@ -37032,7 +37031,7 @@
       <c r="AW288" s="7"/>
       <c r="AX288" s="7"/>
     </row>
-    <row r="289" ht="20.25" hidden="1" customHeight="1">
+    <row r="289" ht="20.25" customHeight="1">
       <c r="A289" s="12">
         <v>1367.0</v>
       </c>
@@ -37140,7 +37139,7 @@
       <c r="AW289" s="7"/>
       <c r="AX289" s="7"/>
     </row>
-    <row r="290" ht="20.25" hidden="1" customHeight="1">
+    <row r="290" ht="20.25" customHeight="1">
       <c r="A290" s="8">
         <v>1368.0</v>
       </c>
@@ -37248,7 +37247,7 @@
       <c r="AW290" s="7"/>
       <c r="AX290" s="7"/>
     </row>
-    <row r="291" ht="20.25" hidden="1" customHeight="1">
+    <row r="291" ht="20.25" customHeight="1">
       <c r="A291" s="12">
         <v>1369.0</v>
       </c>
@@ -37356,7 +37355,7 @@
       <c r="AW291" s="7"/>
       <c r="AX291" s="7"/>
     </row>
-    <row r="292" ht="20.25" hidden="1" customHeight="1">
+    <row r="292" ht="20.25" customHeight="1">
       <c r="A292" s="8">
         <v>1370.0</v>
       </c>
@@ -37464,7 +37463,7 @@
       <c r="AW292" s="7"/>
       <c r="AX292" s="7"/>
     </row>
-    <row r="293" ht="20.25" hidden="1" customHeight="1">
+    <row r="293" ht="20.25" customHeight="1">
       <c r="A293" s="12">
         <v>1371.0</v>
       </c>
@@ -37572,7 +37571,7 @@
       <c r="AW293" s="7"/>
       <c r="AX293" s="7"/>
     </row>
-    <row r="294" ht="20.25" hidden="1" customHeight="1">
+    <row r="294" ht="20.25" customHeight="1">
       <c r="A294" s="8">
         <v>1372.0</v>
       </c>
@@ -37680,7 +37679,7 @@
       <c r="AW294" s="7"/>
       <c r="AX294" s="7"/>
     </row>
-    <row r="295" ht="20.25" hidden="1" customHeight="1">
+    <row r="295" ht="20.25" customHeight="1">
       <c r="A295" s="12">
         <v>1373.0</v>
       </c>
@@ -37788,7 +37787,7 @@
       <c r="AW295" s="7"/>
       <c r="AX295" s="7"/>
     </row>
-    <row r="296" ht="20.25" hidden="1" customHeight="1">
+    <row r="296" ht="20.25" customHeight="1">
       <c r="A296" s="8">
         <v>1374.0</v>
       </c>
@@ -37896,7 +37895,7 @@
       <c r="AW296" s="7"/>
       <c r="AX296" s="7"/>
     </row>
-    <row r="297" ht="20.25" hidden="1" customHeight="1">
+    <row r="297" ht="20.25" customHeight="1">
       <c r="A297" s="12">
         <v>1375.0</v>
       </c>
@@ -38004,7 +38003,7 @@
       <c r="AW297" s="7"/>
       <c r="AX297" s="7"/>
     </row>
-    <row r="298" ht="20.25" hidden="1" customHeight="1">
+    <row r="298" ht="20.25" customHeight="1">
       <c r="A298" s="8">
         <v>1376.0</v>
       </c>
@@ -38112,7 +38111,7 @@
       <c r="AW298" s="7"/>
       <c r="AX298" s="7"/>
     </row>
-    <row r="299" ht="20.25" hidden="1" customHeight="1">
+    <row r="299" ht="20.25" customHeight="1">
       <c r="A299" s="12">
         <v>1377.0</v>
       </c>
@@ -38220,7 +38219,7 @@
       <c r="AW299" s="7"/>
       <c r="AX299" s="7"/>
     </row>
-    <row r="300" ht="20.25" hidden="1" customHeight="1">
+    <row r="300" ht="20.25" customHeight="1">
       <c r="A300" s="8">
         <v>1378.0</v>
       </c>
@@ -38328,7 +38327,7 @@
       <c r="AW300" s="7"/>
       <c r="AX300" s="7"/>
     </row>
-    <row r="301" ht="20.25" hidden="1" customHeight="1">
+    <row r="301" ht="20.25" customHeight="1">
       <c r="A301" s="12">
         <v>1379.0</v>
       </c>
@@ -38436,7 +38435,7 @@
       <c r="AW301" s="7"/>
       <c r="AX301" s="7"/>
     </row>
-    <row r="302" ht="20.25" hidden="1" customHeight="1">
+    <row r="302" ht="20.25" customHeight="1">
       <c r="A302" s="8">
         <v>1380.0</v>
       </c>
@@ -38544,7 +38543,7 @@
       <c r="AW302" s="7"/>
       <c r="AX302" s="7"/>
     </row>
-    <row r="303" ht="20.25" hidden="1" customHeight="1">
+    <row r="303" ht="20.25" customHeight="1">
       <c r="A303" s="12">
         <v>1381.0</v>
       </c>
@@ -38652,7 +38651,7 @@
       <c r="AW303" s="7"/>
       <c r="AX303" s="7"/>
     </row>
-    <row r="304" ht="20.25" hidden="1" customHeight="1">
+    <row r="304" ht="20.25" customHeight="1">
       <c r="A304" s="8">
         <v>1382.0</v>
       </c>
@@ -38760,7 +38759,7 @@
       <c r="AW304" s="7"/>
       <c r="AX304" s="7"/>
     </row>
-    <row r="305" ht="20.25" hidden="1" customHeight="1">
+    <row r="305" ht="20.25" customHeight="1">
       <c r="A305" s="12">
         <v>1383.0</v>
       </c>
@@ -38868,7 +38867,7 @@
       <c r="AW305" s="7"/>
       <c r="AX305" s="7"/>
     </row>
-    <row r="306" ht="20.25" hidden="1" customHeight="1">
+    <row r="306" ht="20.25" customHeight="1">
       <c r="A306" s="8">
         <v>1384.0</v>
       </c>
@@ -38976,7 +38975,7 @@
       <c r="AW306" s="7"/>
       <c r="AX306" s="7"/>
     </row>
-    <row r="307" ht="20.25" hidden="1" customHeight="1">
+    <row r="307" ht="20.25" customHeight="1">
       <c r="A307" s="12">
         <v>1385.0</v>
       </c>
@@ -39084,7 +39083,7 @@
       <c r="AW307" s="7"/>
       <c r="AX307" s="7"/>
     </row>
-    <row r="308" ht="20.25" hidden="1" customHeight="1">
+    <row r="308" ht="20.25" customHeight="1">
       <c r="A308" s="8">
         <v>1386.0</v>
       </c>
@@ -39192,7 +39191,7 @@
       <c r="AW308" s="7"/>
       <c r="AX308" s="7"/>
     </row>
-    <row r="309" ht="20.25" hidden="1" customHeight="1">
+    <row r="309" ht="20.25" customHeight="1">
       <c r="A309" s="12">
         <v>1387.0</v>
       </c>
@@ -39300,7 +39299,7 @@
       <c r="AW309" s="7"/>
       <c r="AX309" s="7"/>
     </row>
-    <row r="310" ht="20.25" hidden="1" customHeight="1">
+    <row r="310" ht="20.25" customHeight="1">
       <c r="A310" s="8">
         <v>1388.0</v>
       </c>
@@ -39408,7 +39407,7 @@
       <c r="AW310" s="7"/>
       <c r="AX310" s="7"/>
     </row>
-    <row r="311" ht="20.25" hidden="1" customHeight="1">
+    <row r="311" ht="20.25" customHeight="1">
       <c r="A311" s="12">
         <v>1389.0</v>
       </c>
@@ -39516,7 +39515,7 @@
       <c r="AW311" s="7"/>
       <c r="AX311" s="7"/>
     </row>
-    <row r="312" ht="20.25" hidden="1" customHeight="1">
+    <row r="312" ht="20.25" customHeight="1">
       <c r="A312" s="8">
         <v>1390.0</v>
       </c>
@@ -39624,7 +39623,7 @@
       <c r="AW312" s="7"/>
       <c r="AX312" s="7"/>
     </row>
-    <row r="313" ht="20.25" hidden="1" customHeight="1">
+    <row r="313" ht="20.25" customHeight="1">
       <c r="A313" s="12">
         <v>1391.0</v>
       </c>
@@ -39732,7 +39731,7 @@
       <c r="AW313" s="7"/>
       <c r="AX313" s="7"/>
     </row>
-    <row r="314" ht="20.25" hidden="1" customHeight="1">
+    <row r="314" ht="20.25" customHeight="1">
       <c r="A314" s="8">
         <v>1392.0</v>
       </c>
@@ -39840,7 +39839,7 @@
       <c r="AW314" s="7"/>
       <c r="AX314" s="7"/>
     </row>
-    <row r="315" ht="20.25" hidden="1" customHeight="1">
+    <row r="315" ht="20.25" customHeight="1">
       <c r="A315" s="12">
         <v>1393.0</v>
       </c>
@@ -39948,7 +39947,7 @@
       <c r="AW315" s="7"/>
       <c r="AX315" s="7"/>
     </row>
-    <row r="316" ht="20.25" hidden="1" customHeight="1">
+    <row r="316" ht="20.25" customHeight="1">
       <c r="A316" s="8">
         <v>1394.0</v>
       </c>
@@ -40056,7 +40055,7 @@
       <c r="AW316" s="7"/>
       <c r="AX316" s="7"/>
     </row>
-    <row r="317" ht="20.25" hidden="1" customHeight="1">
+    <row r="317" ht="20.25" customHeight="1">
       <c r="A317" s="12">
         <v>1395.0</v>
       </c>
@@ -40164,7 +40163,7 @@
       <c r="AW317" s="7"/>
       <c r="AX317" s="7"/>
     </row>
-    <row r="318" ht="20.25" hidden="1" customHeight="1">
+    <row r="318" ht="20.25" customHeight="1">
       <c r="A318" s="8">
         <v>1396.0</v>
       </c>
@@ -40272,7 +40271,7 @@
       <c r="AW318" s="7"/>
       <c r="AX318" s="7"/>
     </row>
-    <row r="319" ht="20.25" hidden="1" customHeight="1">
+    <row r="319" ht="20.25" customHeight="1">
       <c r="A319" s="12">
         <v>1397.0</v>
       </c>
@@ -40382,7 +40381,7 @@
       <c r="AW319" s="7"/>
       <c r="AX319" s="7"/>
     </row>
-    <row r="320" ht="20.25" hidden="1" customHeight="1">
+    <row r="320" ht="20.25" customHeight="1">
       <c r="A320" s="8">
         <v>1398.0</v>
       </c>
@@ -40490,7 +40489,7 @@
       <c r="AW320" s="7"/>
       <c r="AX320" s="7"/>
     </row>
-    <row r="321" ht="20.25" hidden="1" customHeight="1">
+    <row r="321" ht="20.25" customHeight="1">
       <c r="A321" s="12">
         <v>1399.0</v>
       </c>
@@ -40598,7 +40597,7 @@
       <c r="AW321" s="7"/>
       <c r="AX321" s="7"/>
     </row>
-    <row r="322" ht="20.25" hidden="1" customHeight="1">
+    <row r="322" ht="20.25" customHeight="1">
       <c r="A322" s="8">
         <v>1400.0</v>
       </c>
@@ -40708,7 +40707,7 @@
       <c r="AW322" s="7"/>
       <c r="AX322" s="7"/>
     </row>
-    <row r="323" ht="20.25" hidden="1" customHeight="1">
+    <row r="323" ht="20.25" customHeight="1">
       <c r="A323" s="12">
         <v>1401.0</v>
       </c>
@@ -40818,7 +40817,7 @@
       <c r="AW323" s="7"/>
       <c r="AX323" s="7"/>
     </row>
-    <row r="324" ht="20.25" hidden="1" customHeight="1">
+    <row r="324" ht="20.25" customHeight="1">
       <c r="A324" s="8">
         <v>1402.0</v>
       </c>
@@ -40928,7 +40927,7 @@
       <c r="AW324" s="7"/>
       <c r="AX324" s="7"/>
     </row>
-    <row r="325" ht="20.25" hidden="1" customHeight="1">
+    <row r="325" ht="20.25" customHeight="1">
       <c r="A325" s="12">
         <v>1403.0</v>
       </c>
@@ -41038,7 +41037,7 @@
       <c r="AW325" s="7"/>
       <c r="AX325" s="7"/>
     </row>
-    <row r="326" ht="20.25" hidden="1" customHeight="1">
+    <row r="326" ht="20.25" customHeight="1">
       <c r="A326" s="8">
         <v>1404.0</v>
       </c>
@@ -41148,7 +41147,7 @@
       <c r="AW326" s="7"/>
       <c r="AX326" s="7"/>
     </row>
-    <row r="327" ht="20.25" hidden="1" customHeight="1">
+    <row r="327" ht="20.25" customHeight="1">
       <c r="A327" s="12">
         <v>1405.0</v>
       </c>
@@ -41258,7 +41257,7 @@
       <c r="AW327" s="7"/>
       <c r="AX327" s="7"/>
     </row>
-    <row r="328" ht="20.25" hidden="1" customHeight="1">
+    <row r="328" ht="20.25" customHeight="1">
       <c r="A328" s="8">
         <v>1406.0</v>
       </c>
@@ -41368,7 +41367,7 @@
       <c r="AW328" s="7"/>
       <c r="AX328" s="7"/>
     </row>
-    <row r="329" ht="20.25" hidden="1" customHeight="1">
+    <row r="329" ht="20.25" customHeight="1">
       <c r="A329" s="12">
         <v>1407.0</v>
       </c>
@@ -41478,7 +41477,7 @@
       <c r="AW329" s="7"/>
       <c r="AX329" s="7"/>
     </row>
-    <row r="330" ht="20.25" hidden="1" customHeight="1">
+    <row r="330" ht="20.25" customHeight="1">
       <c r="A330" s="8">
         <v>1408.0</v>
       </c>
@@ -41588,7 +41587,7 @@
       <c r="AW330" s="7"/>
       <c r="AX330" s="7"/>
     </row>
-    <row r="331" ht="20.25" hidden="1" customHeight="1">
+    <row r="331" ht="20.25" customHeight="1">
       <c r="A331" s="12">
         <v>1409.0</v>
       </c>
@@ -41696,7 +41695,7 @@
       <c r="AW331" s="7"/>
       <c r="AX331" s="7"/>
     </row>
-    <row r="332" ht="20.25" hidden="1" customHeight="1">
+    <row r="332" ht="20.25" customHeight="1">
       <c r="A332" s="8">
         <v>1410.0</v>
       </c>
@@ -41804,7 +41803,7 @@
       <c r="AW332" s="7"/>
       <c r="AX332" s="7"/>
     </row>
-    <row r="333" ht="20.25" hidden="1" customHeight="1">
+    <row r="333" ht="20.25" customHeight="1">
       <c r="A333" s="12">
         <v>1411.0</v>
       </c>
@@ -41912,7 +41911,7 @@
       <c r="AW333" s="7"/>
       <c r="AX333" s="7"/>
     </row>
-    <row r="334" ht="20.25" hidden="1" customHeight="1">
+    <row r="334" ht="20.25" customHeight="1">
       <c r="A334" s="8">
         <v>1412.0</v>
       </c>
@@ -42020,7 +42019,7 @@
       <c r="AW334" s="7"/>
       <c r="AX334" s="7"/>
     </row>
-    <row r="335" ht="20.25" hidden="1" customHeight="1">
+    <row r="335" ht="20.25" customHeight="1">
       <c r="A335" s="12">
         <v>1413.0</v>
       </c>
@@ -42128,7 +42127,7 @@
       <c r="AW335" s="7"/>
       <c r="AX335" s="7"/>
     </row>
-    <row r="336" ht="20.25" hidden="1" customHeight="1">
+    <row r="336" ht="20.25" customHeight="1">
       <c r="A336" s="8">
         <v>1414.0</v>
       </c>
@@ -42236,7 +42235,7 @@
       <c r="AW336" s="7"/>
       <c r="AX336" s="7"/>
     </row>
-    <row r="337" ht="20.25" hidden="1" customHeight="1">
+    <row r="337" ht="20.25" customHeight="1">
       <c r="A337" s="12">
         <v>1415.0</v>
       </c>
@@ -42344,7 +42343,7 @@
       <c r="AW337" s="7"/>
       <c r="AX337" s="7"/>
     </row>
-    <row r="338" ht="20.25" hidden="1" customHeight="1">
+    <row r="338" ht="20.25" customHeight="1">
       <c r="A338" s="8">
         <v>1416.0</v>
       </c>
@@ -42452,7 +42451,7 @@
       <c r="AW338" s="7"/>
       <c r="AX338" s="7"/>
     </row>
-    <row r="339" ht="20.25" hidden="1" customHeight="1">
+    <row r="339" ht="20.25" customHeight="1">
       <c r="A339" s="12">
         <v>1417.0</v>
       </c>
@@ -42560,7 +42559,7 @@
       <c r="AW339" s="7"/>
       <c r="AX339" s="7"/>
     </row>
-    <row r="340" ht="20.25" hidden="1" customHeight="1">
+    <row r="340" ht="20.25" customHeight="1">
       <c r="A340" s="8">
         <v>1418.0</v>
       </c>
@@ -42668,7 +42667,7 @@
       <c r="AW340" s="7"/>
       <c r="AX340" s="7"/>
     </row>
-    <row r="341" ht="20.25" hidden="1" customHeight="1">
+    <row r="341" ht="20.25" customHeight="1">
       <c r="A341" s="12">
         <v>1419.0</v>
       </c>
@@ -42776,7 +42775,7 @@
       <c r="AW341" s="7"/>
       <c r="AX341" s="7"/>
     </row>
-    <row r="342" ht="20.25" hidden="1" customHeight="1">
+    <row r="342" ht="20.25" customHeight="1">
       <c r="A342" s="8">
         <v>1420.0</v>
       </c>
@@ -42884,7 +42883,7 @@
       <c r="AW342" s="7"/>
       <c r="AX342" s="7"/>
     </row>
-    <row r="343" ht="20.25" hidden="1" customHeight="1">
+    <row r="343" ht="20.25" customHeight="1">
       <c r="A343" s="12">
         <v>1421.0</v>
       </c>
@@ -42992,7 +42991,7 @@
       <c r="AW343" s="7"/>
       <c r="AX343" s="7"/>
     </row>
-    <row r="344" ht="20.25" hidden="1" customHeight="1">
+    <row r="344" ht="20.25" customHeight="1">
       <c r="A344" s="8">
         <v>1422.0</v>
       </c>
@@ -43100,7 +43099,7 @@
       <c r="AW344" s="7"/>
       <c r="AX344" s="7"/>
     </row>
-    <row r="345" ht="20.25" hidden="1" customHeight="1">
+    <row r="345" ht="20.25" customHeight="1">
       <c r="A345" s="12">
         <v>1423.0</v>
       </c>
@@ -43208,7 +43207,7 @@
       <c r="AW345" s="7"/>
       <c r="AX345" s="7"/>
     </row>
-    <row r="346" ht="20.25" hidden="1" customHeight="1">
+    <row r="346" ht="20.25" customHeight="1">
       <c r="A346" s="8">
         <v>1424.0</v>
       </c>
@@ -43316,7 +43315,7 @@
       <c r="AW346" s="7"/>
       <c r="AX346" s="7"/>
     </row>
-    <row r="347" ht="20.25" hidden="1" customHeight="1">
+    <row r="347" ht="20.25" customHeight="1">
       <c r="A347" s="12">
         <v>1425.0</v>
       </c>
@@ -43424,7 +43423,7 @@
       <c r="AW347" s="7"/>
       <c r="AX347" s="7"/>
     </row>
-    <row r="348" ht="20.25" hidden="1" customHeight="1">
+    <row r="348" ht="20.25" customHeight="1">
       <c r="A348" s="8">
         <v>1426.0</v>
       </c>
@@ -43534,7 +43533,7 @@
       <c r="AW348" s="7"/>
       <c r="AX348" s="7"/>
     </row>
-    <row r="349" ht="20.25" hidden="1" customHeight="1">
+    <row r="349" ht="20.25" customHeight="1">
       <c r="A349" s="12">
         <v>1427.0</v>
       </c>
@@ -43642,7 +43641,7 @@
       <c r="AW349" s="7"/>
       <c r="AX349" s="7"/>
     </row>
-    <row r="350" ht="20.25" hidden="1" customHeight="1">
+    <row r="350" ht="20.25" customHeight="1">
       <c r="A350" s="8">
         <v>1428.0</v>
       </c>
@@ -43750,7 +43749,7 @@
       <c r="AW350" s="7"/>
       <c r="AX350" s="7"/>
     </row>
-    <row r="351" ht="20.25" hidden="1" customHeight="1">
+    <row r="351" ht="20.25" customHeight="1">
       <c r="A351" s="12">
         <v>1429.0</v>
       </c>
@@ -43858,7 +43857,7 @@
       <c r="AW351" s="7"/>
       <c r="AX351" s="7"/>
     </row>
-    <row r="352" ht="20.25" hidden="1" customHeight="1">
+    <row r="352" ht="20.25" customHeight="1">
       <c r="A352" s="8">
         <v>1430.0</v>
       </c>
@@ -43966,7 +43965,7 @@
       <c r="AW352" s="7"/>
       <c r="AX352" s="7"/>
     </row>
-    <row r="353" ht="20.25" hidden="1" customHeight="1">
+    <row r="353" ht="20.25" customHeight="1">
       <c r="A353" s="12">
         <v>1431.0</v>
       </c>
@@ -44074,7 +44073,7 @@
       <c r="AW353" s="7"/>
       <c r="AX353" s="7"/>
     </row>
-    <row r="354" ht="20.25" hidden="1" customHeight="1">
+    <row r="354" ht="20.25" customHeight="1">
       <c r="A354" s="8">
         <v>1432.0</v>
       </c>
@@ -44182,7 +44181,7 @@
       <c r="AW354" s="7"/>
       <c r="AX354" s="7"/>
     </row>
-    <row r="355" ht="20.25" hidden="1" customHeight="1">
+    <row r="355" ht="20.25" customHeight="1">
       <c r="A355" s="12">
         <v>1433.0</v>
       </c>
@@ -44290,7 +44289,7 @@
       <c r="AW355" s="7"/>
       <c r="AX355" s="7"/>
     </row>
-    <row r="356" ht="20.25" hidden="1" customHeight="1">
+    <row r="356" ht="20.25" customHeight="1">
       <c r="A356" s="8">
         <v>1434.0</v>
       </c>
@@ -44398,7 +44397,7 @@
       <c r="AW356" s="7"/>
       <c r="AX356" s="7"/>
     </row>
-    <row r="357" ht="20.25" hidden="1" customHeight="1">
+    <row r="357" ht="20.25" customHeight="1">
       <c r="A357" s="12">
         <v>1435.0</v>
       </c>
@@ -44506,7 +44505,7 @@
       <c r="AW357" s="7"/>
       <c r="AX357" s="7"/>
     </row>
-    <row r="358" ht="20.25" hidden="1" customHeight="1">
+    <row r="358" ht="20.25" customHeight="1">
       <c r="A358" s="8">
         <v>1436.0</v>
       </c>
@@ -44614,7 +44613,7 @@
       <c r="AW358" s="7"/>
       <c r="AX358" s="7"/>
     </row>
-    <row r="359" ht="20.25" hidden="1" customHeight="1">
+    <row r="359" ht="20.25" customHeight="1">
       <c r="A359" s="12">
         <v>1437.0</v>
       </c>
@@ -44722,7 +44721,7 @@
       <c r="AW359" s="7"/>
       <c r="AX359" s="7"/>
     </row>
-    <row r="360" ht="20.25" hidden="1" customHeight="1">
+    <row r="360" ht="20.25" customHeight="1">
       <c r="A360" s="8">
         <v>1438.0</v>
       </c>
@@ -44832,7 +44831,7 @@
       <c r="AW360" s="7"/>
       <c r="AX360" s="7"/>
     </row>
-    <row r="361" ht="20.25" hidden="1" customHeight="1">
+    <row r="361" ht="20.25" customHeight="1">
       <c r="A361" s="12">
         <v>1439.0</v>
       </c>
@@ -44942,7 +44941,7 @@
       <c r="AW361" s="7"/>
       <c r="AX361" s="7"/>
     </row>
-    <row r="362" ht="20.25" hidden="1" customHeight="1">
+    <row r="362" ht="20.25" customHeight="1">
       <c r="A362" s="8">
         <v>1440.0</v>
       </c>
@@ -45052,7 +45051,7 @@
       <c r="AW362" s="7"/>
       <c r="AX362" s="7"/>
     </row>
-    <row r="363" ht="20.25" hidden="1" customHeight="1">
+    <row r="363" ht="20.25" customHeight="1">
       <c r="A363" s="12">
         <v>1441.0</v>
       </c>
@@ -45162,7 +45161,7 @@
       <c r="AW363" s="7"/>
       <c r="AX363" s="7"/>
     </row>
-    <row r="364" ht="20.25" hidden="1" customHeight="1">
+    <row r="364" ht="20.25" customHeight="1">
       <c r="A364" s="8">
         <v>1442.0</v>
       </c>
@@ -45272,7 +45271,7 @@
       <c r="AW364" s="7"/>
       <c r="AX364" s="7"/>
     </row>
-    <row r="365" ht="20.25" hidden="1" customHeight="1">
+    <row r="365" ht="20.25" customHeight="1">
       <c r="A365" s="12">
         <v>1443.0</v>
       </c>
@@ -45382,7 +45381,7 @@
       <c r="AW365" s="7"/>
       <c r="AX365" s="7"/>
     </row>
-    <row r="366" ht="20.25" hidden="1" customHeight="1">
+    <row r="366" ht="20.25" customHeight="1">
       <c r="A366" s="8">
         <v>1444.0</v>
       </c>
@@ -45492,7 +45491,7 @@
       <c r="AW366" s="7"/>
       <c r="AX366" s="7"/>
     </row>
-    <row r="367" ht="20.25" hidden="1" customHeight="1">
+    <row r="367" ht="20.25" customHeight="1">
       <c r="A367" s="12">
         <v>1445.0</v>
       </c>
@@ -45602,7 +45601,7 @@
       <c r="AW367" s="7"/>
       <c r="AX367" s="7"/>
     </row>
-    <row r="368" ht="20.25" hidden="1" customHeight="1">
+    <row r="368" ht="20.25" customHeight="1">
       <c r="A368" s="8">
         <v>1446.0</v>
       </c>
@@ -45712,7 +45711,7 @@
       <c r="AW368" s="7"/>
       <c r="AX368" s="7"/>
     </row>
-    <row r="369" ht="20.25" hidden="1" customHeight="1">
+    <row r="369" ht="20.25" customHeight="1">
       <c r="A369" s="12">
         <v>1447.0</v>
       </c>
@@ -45822,7 +45821,7 @@
       <c r="AW369" s="7"/>
       <c r="AX369" s="7"/>
     </row>
-    <row r="370" ht="20.25" hidden="1" customHeight="1">
+    <row r="370" ht="20.25" customHeight="1">
       <c r="A370" s="8">
         <v>1448.0</v>
       </c>
@@ -45932,7 +45931,7 @@
       <c r="AW370" s="7"/>
       <c r="AX370" s="7"/>
     </row>
-    <row r="371" ht="20.25" hidden="1" customHeight="1">
+    <row r="371" ht="20.25" customHeight="1">
       <c r="A371" s="12">
         <v>1449.0</v>
       </c>
@@ -46040,7 +46039,7 @@
       <c r="AW371" s="7"/>
       <c r="AX371" s="7"/>
     </row>
-    <row r="372" ht="20.25" hidden="1" customHeight="1">
+    <row r="372" ht="20.25" customHeight="1">
       <c r="A372" s="8">
         <v>1450.0</v>
       </c>
@@ -46148,7 +46147,7 @@
       <c r="AW372" s="7"/>
       <c r="AX372" s="7"/>
     </row>
-    <row r="373" ht="20.25" hidden="1" customHeight="1">
+    <row r="373" ht="20.25" customHeight="1">
       <c r="A373" s="12">
         <v>1451.0</v>
       </c>
@@ -46258,7 +46257,7 @@
       <c r="AW373" s="7"/>
       <c r="AX373" s="7"/>
     </row>
-    <row r="374" ht="20.25" hidden="1" customHeight="1">
+    <row r="374" ht="20.25" customHeight="1">
       <c r="A374" s="8">
         <v>1452.0</v>
       </c>
@@ -46366,7 +46365,7 @@
       <c r="AW374" s="7"/>
       <c r="AX374" s="7"/>
     </row>
-    <row r="375" ht="20.25" hidden="1" customHeight="1">
+    <row r="375" ht="20.25" customHeight="1">
       <c r="A375" s="12">
         <v>1453.0</v>
       </c>
@@ -46474,7 +46473,7 @@
       <c r="AW375" s="7"/>
       <c r="AX375" s="7"/>
     </row>
-    <row r="376" ht="20.25" hidden="1" customHeight="1">
+    <row r="376" ht="20.25" customHeight="1">
       <c r="A376" s="8">
         <v>1454.0</v>
       </c>
@@ -46582,7 +46581,7 @@
       <c r="AW376" s="7"/>
       <c r="AX376" s="7"/>
     </row>
-    <row r="377" ht="20.25" hidden="1" customHeight="1">
+    <row r="377" ht="20.25" customHeight="1">
       <c r="A377" s="12">
         <v>1455.0</v>
       </c>
@@ -46690,7 +46689,7 @@
       <c r="AW377" s="7"/>
       <c r="AX377" s="7"/>
     </row>
-    <row r="378" ht="20.25" hidden="1" customHeight="1">
+    <row r="378" ht="20.25" customHeight="1">
       <c r="A378" s="8">
         <v>1456.0</v>
       </c>
@@ -46798,7 +46797,7 @@
       <c r="AW378" s="7"/>
       <c r="AX378" s="7"/>
     </row>
-    <row r="379" ht="20.25" hidden="1" customHeight="1">
+    <row r="379" ht="20.25" customHeight="1">
       <c r="A379" s="12">
         <v>1457.0</v>
       </c>
@@ -46906,7 +46905,7 @@
       <c r="AW379" s="7"/>
       <c r="AX379" s="7"/>
     </row>
-    <row r="380" ht="20.25" hidden="1" customHeight="1">
+    <row r="380" ht="20.25" customHeight="1">
       <c r="A380" s="8">
         <v>1458.0</v>
       </c>
@@ -47014,7 +47013,7 @@
       <c r="AW380" s="7"/>
       <c r="AX380" s="7"/>
     </row>
-    <row r="381" ht="20.25" hidden="1" customHeight="1">
+    <row r="381" ht="20.25" customHeight="1">
       <c r="A381" s="12">
         <v>1459.0</v>
       </c>
@@ -47122,7 +47121,7 @@
       <c r="AW381" s="7"/>
       <c r="AX381" s="7"/>
     </row>
-    <row r="382" ht="20.25" hidden="1" customHeight="1">
+    <row r="382" ht="20.25" customHeight="1">
       <c r="A382" s="8">
         <v>1460.0</v>
       </c>
@@ -47232,7 +47231,7 @@
       <c r="AW382" s="7"/>
       <c r="AX382" s="7"/>
     </row>
-    <row r="383" ht="20.25" hidden="1" customHeight="1">
+    <row r="383" ht="20.25" customHeight="1">
       <c r="A383" s="12">
         <v>1461.0</v>
       </c>
@@ -47342,7 +47341,7 @@
       <c r="AW383" s="7"/>
       <c r="AX383" s="7"/>
     </row>
-    <row r="384" ht="20.25" hidden="1" customHeight="1">
+    <row r="384" ht="20.25" customHeight="1">
       <c r="A384" s="8">
         <v>1463.0</v>
       </c>
@@ -47452,7 +47451,7 @@
       <c r="AW384" s="7"/>
       <c r="AX384" s="7"/>
     </row>
-    <row r="385" ht="20.25" hidden="1" customHeight="1">
+    <row r="385" ht="20.25" customHeight="1">
       <c r="A385" s="12">
         <v>1464.0</v>
       </c>
@@ -47562,7 +47561,7 @@
       <c r="AW385" s="7"/>
       <c r="AX385" s="7"/>
     </row>
-    <row r="386" ht="20.25" hidden="1" customHeight="1">
+    <row r="386" ht="20.25" customHeight="1">
       <c r="A386" s="8">
         <v>1465.0</v>
       </c>
@@ -47670,7 +47669,7 @@
       <c r="AW386" s="7"/>
       <c r="AX386" s="7"/>
     </row>
-    <row r="387" ht="20.25" hidden="1" customHeight="1">
+    <row r="387" ht="20.25" customHeight="1">
       <c r="A387" s="12">
         <v>1466.0</v>
       </c>
@@ -47778,7 +47777,7 @@
       <c r="AW387" s="7"/>
       <c r="AX387" s="7"/>
     </row>
-    <row r="388" ht="20.25" hidden="1" customHeight="1">
+    <row r="388" ht="20.25" customHeight="1">
       <c r="A388" s="8">
         <v>1467.0</v>
       </c>
@@ -47886,7 +47885,7 @@
       <c r="AW388" s="7"/>
       <c r="AX388" s="7"/>
     </row>
-    <row r="389" ht="20.25" hidden="1" customHeight="1">
+    <row r="389" ht="20.25" customHeight="1">
       <c r="A389" s="12">
         <v>1468.0</v>
       </c>
@@ -47994,7 +47993,7 @@
       <c r="AW389" s="7"/>
       <c r="AX389" s="7"/>
     </row>
-    <row r="390" ht="20.25" hidden="1" customHeight="1">
+    <row r="390" ht="20.25" customHeight="1">
       <c r="A390" s="8">
         <v>1469.0</v>
       </c>
@@ -48102,7 +48101,7 @@
       <c r="AW390" s="7"/>
       <c r="AX390" s="7"/>
     </row>
-    <row r="391" ht="20.25" hidden="1" customHeight="1">
+    <row r="391" ht="20.25" customHeight="1">
       <c r="A391" s="12">
         <v>1470.0</v>
       </c>
@@ -48210,7 +48209,7 @@
       <c r="AW391" s="7"/>
       <c r="AX391" s="7"/>
     </row>
-    <row r="392" ht="20.25" hidden="1" customHeight="1">
+    <row r="392" ht="20.25" customHeight="1">
       <c r="A392" s="8">
         <v>1471.0</v>
       </c>
@@ -48318,7 +48317,7 @@
       <c r="AW392" s="7"/>
       <c r="AX392" s="7"/>
     </row>
-    <row r="393" ht="20.25" hidden="1" customHeight="1">
+    <row r="393" ht="20.25" customHeight="1">
       <c r="A393" s="12">
         <v>1472.0</v>
       </c>
@@ -48426,7 +48425,7 @@
       <c r="AW393" s="7"/>
       <c r="AX393" s="7"/>
     </row>
-    <row r="394" ht="20.25" hidden="1" customHeight="1">
+    <row r="394" ht="20.25" customHeight="1">
       <c r="A394" s="8">
         <v>1473.0</v>
       </c>
@@ -48534,7 +48533,7 @@
       <c r="AW394" s="7"/>
       <c r="AX394" s="7"/>
     </row>
-    <row r="395" ht="20.25" hidden="1" customHeight="1">
+    <row r="395" ht="20.25" customHeight="1">
       <c r="A395" s="12">
         <v>1474.0</v>
       </c>
@@ -48642,7 +48641,7 @@
       <c r="AW395" s="7"/>
       <c r="AX395" s="7"/>
     </row>
-    <row r="396" ht="20.25" hidden="1" customHeight="1">
+    <row r="396" ht="20.25" customHeight="1">
       <c r="A396" s="8">
         <v>1475.0</v>
       </c>
@@ -48750,7 +48749,7 @@
       <c r="AW396" s="7"/>
       <c r="AX396" s="7"/>
     </row>
-    <row r="397" ht="20.25" hidden="1" customHeight="1">
+    <row r="397" ht="20.25" customHeight="1">
       <c r="A397" s="12">
         <v>1476.0</v>
       </c>
@@ -48858,7 +48857,7 @@
       <c r="AW397" s="7"/>
       <c r="AX397" s="7"/>
     </row>
-    <row r="398" ht="20.25" hidden="1" customHeight="1">
+    <row r="398" ht="20.25" customHeight="1">
       <c r="A398" s="8">
         <v>1477.0</v>
       </c>
@@ -48966,7 +48965,7 @@
       <c r="AW398" s="7"/>
       <c r="AX398" s="7"/>
     </row>
-    <row r="399" ht="20.25" hidden="1" customHeight="1">
+    <row r="399" ht="20.25" customHeight="1">
       <c r="A399" s="12">
         <v>1478.0</v>
       </c>
@@ -49074,7 +49073,7 @@
       <c r="AW399" s="7"/>
       <c r="AX399" s="7"/>
     </row>
-    <row r="400" ht="20.25" hidden="1" customHeight="1">
+    <row r="400" ht="20.25" customHeight="1">
       <c r="A400" s="8">
         <v>1479.0</v>
       </c>
@@ -49182,7 +49181,7 @@
       <c r="AW400" s="7"/>
       <c r="AX400" s="7"/>
     </row>
-    <row r="401" ht="20.25" hidden="1" customHeight="1">
+    <row r="401" ht="20.25" customHeight="1">
       <c r="A401" s="12">
         <v>1480.0</v>
       </c>
@@ -49290,7 +49289,7 @@
       <c r="AW401" s="7"/>
       <c r="AX401" s="7"/>
     </row>
-    <row r="402" ht="20.25" hidden="1" customHeight="1">
+    <row r="402" ht="20.25" customHeight="1">
       <c r="A402" s="8">
         <v>1481.0</v>
       </c>
@@ -49398,7 +49397,7 @@
       <c r="AW402" s="7"/>
       <c r="AX402" s="7"/>
     </row>
-    <row r="403" ht="20.25" hidden="1" customHeight="1">
+    <row r="403" ht="20.25" customHeight="1">
       <c r="A403" s="12">
         <v>1482.0</v>
       </c>
@@ -49506,7 +49505,7 @@
       <c r="AW403" s="7"/>
       <c r="AX403" s="7"/>
     </row>
-    <row r="404" ht="20.25" hidden="1" customHeight="1">
+    <row r="404" ht="20.25" customHeight="1">
       <c r="A404" s="8">
         <v>1483.0</v>
       </c>
@@ -49614,7 +49613,7 @@
       <c r="AW404" s="7"/>
       <c r="AX404" s="7"/>
     </row>
-    <row r="405" ht="20.25" hidden="1" customHeight="1">
+    <row r="405" ht="20.25" customHeight="1">
       <c r="A405" s="12">
         <v>1484.0</v>
       </c>
@@ -49722,7 +49721,7 @@
       <c r="AW405" s="7"/>
       <c r="AX405" s="7"/>
     </row>
-    <row r="406" ht="20.25" hidden="1" customHeight="1">
+    <row r="406" ht="20.25" customHeight="1">
       <c r="A406" s="8">
         <v>1485.0</v>
       </c>
@@ -49830,7 +49829,7 @@
       <c r="AW406" s="7"/>
       <c r="AX406" s="7"/>
     </row>
-    <row r="407" ht="20.25" hidden="1" customHeight="1">
+    <row r="407" ht="20.25" customHeight="1">
       <c r="A407" s="12">
         <v>1486.0</v>
       </c>
@@ -49938,7 +49937,7 @@
       <c r="AW407" s="7"/>
       <c r="AX407" s="7"/>
     </row>
-    <row r="408" ht="20.25" hidden="1" customHeight="1">
+    <row r="408" ht="20.25" customHeight="1">
       <c r="A408" s="8">
         <v>1487.0</v>
       </c>
@@ -50046,7 +50045,7 @@
       <c r="AW408" s="7"/>
       <c r="AX408" s="7"/>
     </row>
-    <row r="409" ht="20.25" hidden="1" customHeight="1">
+    <row r="409" ht="20.25" customHeight="1">
       <c r="A409" s="12">
         <v>1488.0</v>
       </c>
@@ -50154,7 +50153,7 @@
       <c r="AW409" s="7"/>
       <c r="AX409" s="7"/>
     </row>
-    <row r="410" ht="20.25" hidden="1" customHeight="1">
+    <row r="410" ht="20.25" customHeight="1">
       <c r="A410" s="8">
         <v>1489.0</v>
       </c>
@@ -50262,7 +50261,7 @@
       <c r="AW410" s="7"/>
       <c r="AX410" s="7"/>
     </row>
-    <row r="411" ht="20.25" hidden="1" customHeight="1">
+    <row r="411" ht="20.25" customHeight="1">
       <c r="A411" s="12">
         <v>1490.0</v>
       </c>
@@ -50370,7 +50369,7 @@
       <c r="AW411" s="7"/>
       <c r="AX411" s="7"/>
     </row>
-    <row r="412" ht="20.25" hidden="1" customHeight="1">
+    <row r="412" ht="20.25" customHeight="1">
       <c r="A412" s="8">
         <v>1491.0</v>
       </c>
@@ -50478,7 +50477,7 @@
       <c r="AW412" s="7"/>
       <c r="AX412" s="7"/>
     </row>
-    <row r="413" ht="20.25" hidden="1" customHeight="1">
+    <row r="413" ht="20.25" customHeight="1">
       <c r="A413" s="12">
         <v>1492.0</v>
       </c>
@@ -50588,7 +50587,7 @@
       <c r="AW413" s="7"/>
       <c r="AX413" s="7"/>
     </row>
-    <row r="414" ht="20.25" hidden="1" customHeight="1">
+    <row r="414" ht="20.25" customHeight="1">
       <c r="A414" s="8">
         <v>1493.0</v>
       </c>
@@ -50698,7 +50697,7 @@
       <c r="AW414" s="7"/>
       <c r="AX414" s="7"/>
     </row>
-    <row r="415" ht="20.25" hidden="1" customHeight="1">
+    <row r="415" ht="20.25" customHeight="1">
       <c r="A415" s="12">
         <v>1494.0</v>
       </c>
@@ -50808,7 +50807,7 @@
       <c r="AW415" s="7"/>
       <c r="AX415" s="7"/>
     </row>
-    <row r="416" ht="20.25" hidden="1" customHeight="1">
+    <row r="416" ht="20.25" customHeight="1">
       <c r="A416" s="8">
         <v>1495.0</v>
       </c>
@@ -50918,7 +50917,7 @@
       <c r="AW416" s="7"/>
       <c r="AX416" s="7"/>
     </row>
-    <row r="417" ht="20.25" hidden="1" customHeight="1">
+    <row r="417" ht="20.25" customHeight="1">
       <c r="A417" s="12">
         <v>1496.0</v>
       </c>
@@ -51028,7 +51027,7 @@
       <c r="AW417" s="7"/>
       <c r="AX417" s="7"/>
     </row>
-    <row r="418" ht="20.25" hidden="1" customHeight="1">
+    <row r="418" ht="20.25" customHeight="1">
       <c r="A418" s="8">
         <v>1497.0</v>
       </c>
@@ -51136,7 +51135,7 @@
       <c r="AW418" s="7"/>
       <c r="AX418" s="7"/>
     </row>
-    <row r="419" ht="20.25" hidden="1" customHeight="1">
+    <row r="419" ht="20.25" customHeight="1">
       <c r="A419" s="12">
         <v>1498.0</v>
       </c>
@@ -51244,7 +51243,7 @@
       <c r="AW419" s="7"/>
       <c r="AX419" s="7"/>
     </row>
-    <row r="420" ht="20.25" hidden="1" customHeight="1">
+    <row r="420" ht="20.25" customHeight="1">
       <c r="A420" s="8">
         <v>1499.0</v>
       </c>
@@ -51352,7 +51351,7 @@
       <c r="AW420" s="7"/>
       <c r="AX420" s="7"/>
     </row>
-    <row r="421" ht="20.25" hidden="1" customHeight="1">
+    <row r="421" ht="20.25" customHeight="1">
       <c r="A421" s="12">
         <v>1500.0</v>
       </c>
@@ -51460,7 +51459,7 @@
       <c r="AW421" s="7"/>
       <c r="AX421" s="7"/>
     </row>
-    <row r="422" ht="20.25" hidden="1" customHeight="1">
+    <row r="422" ht="20.25" customHeight="1">
       <c r="A422" s="8">
         <v>1501.0</v>
       </c>
@@ -51568,7 +51567,7 @@
       <c r="AW422" s="7"/>
       <c r="AX422" s="7"/>
     </row>
-    <row r="423" ht="20.25" hidden="1" customHeight="1">
+    <row r="423" ht="20.25" customHeight="1">
       <c r="A423" s="12">
         <v>1502.0</v>
       </c>
@@ -51676,7 +51675,7 @@
       <c r="AW423" s="7"/>
       <c r="AX423" s="7"/>
     </row>
-    <row r="424" ht="20.25" hidden="1" customHeight="1">
+    <row r="424" ht="20.25" customHeight="1">
       <c r="A424" s="8">
         <v>1503.0</v>
       </c>
@@ -51784,7 +51783,7 @@
       <c r="AW424" s="7"/>
       <c r="AX424" s="7"/>
     </row>
-    <row r="425" ht="20.25" hidden="1" customHeight="1">
+    <row r="425" ht="20.25" customHeight="1">
       <c r="A425" s="12">
         <v>1504.0</v>
       </c>
@@ -51892,7 +51891,7 @@
       <c r="AW425" s="7"/>
       <c r="AX425" s="7"/>
     </row>
-    <row r="426" ht="20.25" hidden="1" customHeight="1">
+    <row r="426" ht="20.25" customHeight="1">
       <c r="A426" s="8">
         <v>1505.0</v>
       </c>
@@ -52000,7 +51999,7 @@
       <c r="AW426" s="7"/>
       <c r="AX426" s="7"/>
     </row>
-    <row r="427" ht="20.25" hidden="1" customHeight="1">
+    <row r="427" ht="20.25" customHeight="1">
       <c r="A427" s="12">
         <v>1506.0</v>
       </c>
@@ -52108,7 +52107,7 @@
       <c r="AW427" s="7"/>
       <c r="AX427" s="7"/>
     </row>
-    <row r="428" ht="20.25" hidden="1" customHeight="1">
+    <row r="428" ht="20.25" customHeight="1">
       <c r="A428" s="8">
         <v>1507.0</v>
       </c>
@@ -52216,7 +52215,7 @@
       <c r="AW428" s="7"/>
       <c r="AX428" s="7"/>
     </row>
-    <row r="429" ht="20.25" hidden="1" customHeight="1">
+    <row r="429" ht="20.25" customHeight="1">
       <c r="A429" s="12">
         <v>1508.0</v>
       </c>
@@ -52324,7 +52323,7 @@
       <c r="AW429" s="7"/>
       <c r="AX429" s="7"/>
     </row>
-    <row r="430" ht="20.25" hidden="1" customHeight="1">
+    <row r="430" ht="20.25" customHeight="1">
       <c r="A430" s="8">
         <v>1509.0</v>
       </c>
@@ -52432,7 +52431,7 @@
       <c r="AW430" s="7"/>
       <c r="AX430" s="7"/>
     </row>
-    <row r="431" ht="20.25" hidden="1" customHeight="1">
+    <row r="431" ht="20.25" customHeight="1">
       <c r="A431" s="12">
         <v>1510.0</v>
       </c>
@@ -52540,7 +52539,7 @@
       <c r="AW431" s="7"/>
       <c r="AX431" s="7"/>
     </row>
-    <row r="432" ht="20.25" hidden="1" customHeight="1">
+    <row r="432" ht="20.25" customHeight="1">
       <c r="A432" s="8">
         <v>1511.0</v>
       </c>
@@ -52648,7 +52647,7 @@
       <c r="AW432" s="7"/>
       <c r="AX432" s="7"/>
     </row>
-    <row r="433" ht="20.25" hidden="1" customHeight="1">
+    <row r="433" ht="20.25" customHeight="1">
       <c r="A433" s="12">
         <v>1512.0</v>
       </c>
@@ -52756,7 +52755,7 @@
       <c r="AW433" s="7"/>
       <c r="AX433" s="7"/>
     </row>
-    <row r="434" ht="20.25" hidden="1" customHeight="1">
+    <row r="434" ht="20.25" customHeight="1">
       <c r="A434" s="8">
         <v>1513.0</v>
       </c>
@@ -52864,7 +52863,7 @@
       <c r="AW434" s="7"/>
       <c r="AX434" s="7"/>
     </row>
-    <row r="435" ht="20.25" hidden="1" customHeight="1">
+    <row r="435" ht="20.25" customHeight="1">
       <c r="A435" s="12">
         <v>1514.0</v>
       </c>
@@ -52972,7 +52971,7 @@
       <c r="AW435" s="7"/>
       <c r="AX435" s="7"/>
     </row>
-    <row r="436" ht="20.25" hidden="1" customHeight="1">
+    <row r="436" ht="20.25" customHeight="1">
       <c r="A436" s="8">
         <v>1515.0</v>
       </c>
@@ -53080,7 +53079,7 @@
       <c r="AW436" s="7"/>
       <c r="AX436" s="7"/>
     </row>
-    <row r="437" ht="20.25" hidden="1" customHeight="1">
+    <row r="437" ht="20.25" customHeight="1">
       <c r="A437" s="12">
         <v>1516.0</v>
       </c>
@@ -53188,7 +53187,7 @@
       <c r="AW437" s="7"/>
       <c r="AX437" s="7"/>
     </row>
-    <row r="438" ht="20.25" hidden="1" customHeight="1">
+    <row r="438" ht="20.25" customHeight="1">
       <c r="A438" s="8">
         <v>1517.0</v>
       </c>
@@ -53296,7 +53295,7 @@
       <c r="AW438" s="7"/>
       <c r="AX438" s="7"/>
     </row>
-    <row r="439" ht="20.25" hidden="1" customHeight="1">
+    <row r="439" ht="20.25" customHeight="1">
       <c r="A439" s="12">
         <v>1518.0</v>
       </c>
@@ -53404,7 +53403,7 @@
       <c r="AW439" s="7"/>
       <c r="AX439" s="7"/>
     </row>
-    <row r="440" ht="20.25" hidden="1" customHeight="1">
+    <row r="440" ht="20.25" customHeight="1">
       <c r="A440" s="8">
         <v>1519.0</v>
       </c>
@@ -53512,7 +53511,7 @@
       <c r="AW440" s="7"/>
       <c r="AX440" s="7"/>
     </row>
-    <row r="441" ht="20.25" hidden="1" customHeight="1">
+    <row r="441" ht="20.25" customHeight="1">
       <c r="A441" s="12">
         <v>1520.0</v>
       </c>
@@ -53620,7 +53619,7 @@
       <c r="AW441" s="7"/>
       <c r="AX441" s="7"/>
     </row>
-    <row r="442" ht="20.25" hidden="1" customHeight="1">
+    <row r="442" ht="20.25" customHeight="1">
       <c r="A442" s="8">
         <v>1521.0</v>
       </c>
@@ -53728,7 +53727,7 @@
       <c r="AW442" s="7"/>
       <c r="AX442" s="7"/>
     </row>
-    <row r="443" ht="20.25" hidden="1" customHeight="1">
+    <row r="443" ht="20.25" customHeight="1">
       <c r="A443" s="12">
         <v>1522.0</v>
       </c>
@@ -53836,7 +53835,7 @@
       <c r="AW443" s="7"/>
       <c r="AX443" s="7"/>
     </row>
-    <row r="444" ht="20.25" hidden="1" customHeight="1">
+    <row r="444" ht="20.25" customHeight="1">
       <c r="A444" s="8">
         <v>1523.0</v>
       </c>
@@ -53944,7 +53943,7 @@
       <c r="AW444" s="7"/>
       <c r="AX444" s="7"/>
     </row>
-    <row r="445" ht="20.25" hidden="1" customHeight="1">
+    <row r="445" ht="20.25" customHeight="1">
       <c r="A445" s="12">
         <v>1524.0</v>
       </c>
@@ -54052,7 +54051,7 @@
       <c r="AW445" s="7"/>
       <c r="AX445" s="7"/>
     </row>
-    <row r="446" ht="20.25" hidden="1" customHeight="1">
+    <row r="446" ht="20.25" customHeight="1">
       <c r="A446" s="8">
         <v>1525.0</v>
       </c>
@@ -54162,7 +54161,7 @@
       <c r="AW446" s="7"/>
       <c r="AX446" s="7"/>
     </row>
-    <row r="447" ht="20.25" hidden="1" customHeight="1">
+    <row r="447" ht="20.25" customHeight="1">
       <c r="A447" s="12">
         <v>1526.0</v>
       </c>
@@ -54272,7 +54271,7 @@
       <c r="AW447" s="7"/>
       <c r="AX447" s="7"/>
     </row>
-    <row r="448" ht="20.25" hidden="1" customHeight="1">
+    <row r="448" ht="20.25" customHeight="1">
       <c r="A448" s="8">
         <v>1527.0</v>
       </c>
@@ -54380,7 +54379,7 @@
       <c r="AW448" s="7"/>
       <c r="AX448" s="7"/>
     </row>
-    <row r="449" ht="20.25" hidden="1" customHeight="1">
+    <row r="449" ht="20.25" customHeight="1">
       <c r="A449" s="12">
         <v>1528.0</v>
       </c>
@@ -54488,7 +54487,7 @@
       <c r="AW449" s="7"/>
       <c r="AX449" s="7"/>
     </row>
-    <row r="450" ht="20.25" hidden="1" customHeight="1">
+    <row r="450" ht="20.25" customHeight="1">
       <c r="A450" s="8">
         <v>1529.0</v>
       </c>
@@ -54596,7 +54595,7 @@
       <c r="AW450" s="7"/>
       <c r="AX450" s="7"/>
     </row>
-    <row r="451" ht="20.25" hidden="1" customHeight="1">
+    <row r="451" ht="20.25" customHeight="1">
       <c r="A451" s="12">
         <v>1530.0</v>
       </c>
@@ -54704,7 +54703,7 @@
       <c r="AW451" s="7"/>
       <c r="AX451" s="7"/>
     </row>
-    <row r="452" ht="20.25" hidden="1" customHeight="1">
+    <row r="452" ht="20.25" customHeight="1">
       <c r="A452" s="8">
         <v>1531.0</v>
       </c>
@@ -54812,7 +54811,7 @@
       <c r="AW452" s="7"/>
       <c r="AX452" s="7"/>
     </row>
-    <row r="453" ht="20.25" hidden="1" customHeight="1">
+    <row r="453" ht="20.25" customHeight="1">
       <c r="A453" s="12">
         <v>1532.0</v>
       </c>
@@ -54920,7 +54919,7 @@
       <c r="AW453" s="7"/>
       <c r="AX453" s="7"/>
     </row>
-    <row r="454" ht="20.25" hidden="1" customHeight="1">
+    <row r="454" ht="20.25" customHeight="1">
       <c r="A454" s="8">
         <v>1533.0</v>
       </c>
@@ -55028,7 +55027,7 @@
       <c r="AW454" s="7"/>
       <c r="AX454" s="7"/>
     </row>
-    <row r="455" ht="20.25" hidden="1" customHeight="1">
+    <row r="455" ht="20.25" customHeight="1">
       <c r="A455" s="12">
         <v>1534.0</v>
       </c>
@@ -55136,7 +55135,7 @@
       <c r="AW455" s="7"/>
       <c r="AX455" s="7"/>
     </row>
-    <row r="456" ht="20.25" hidden="1" customHeight="1">
+    <row r="456" ht="20.25" customHeight="1">
       <c r="A456" s="8">
         <v>1535.0</v>
       </c>
@@ -55244,7 +55243,7 @@
       <c r="AW456" s="7"/>
       <c r="AX456" s="7"/>
     </row>
-    <row r="457" ht="20.25" hidden="1" customHeight="1">
+    <row r="457" ht="20.25" customHeight="1">
       <c r="A457" s="12">
         <v>1536.0</v>
       </c>
@@ -55352,7 +55351,7 @@
       <c r="AW457" s="7"/>
       <c r="AX457" s="7"/>
     </row>
-    <row r="458" ht="20.25" hidden="1" customHeight="1">
+    <row r="458" ht="20.25" customHeight="1">
       <c r="A458" s="8">
         <v>1537.0</v>
       </c>
@@ -55460,7 +55459,7 @@
       <c r="AW458" s="7"/>
       <c r="AX458" s="7"/>
     </row>
-    <row r="459" ht="20.25" hidden="1" customHeight="1">
+    <row r="459" ht="20.25" customHeight="1">
       <c r="A459" s="12">
         <v>1538.0</v>
       </c>
@@ -55568,7 +55567,7 @@
       <c r="AW459" s="7"/>
       <c r="AX459" s="7"/>
     </row>
-    <row r="460" ht="20.25" hidden="1" customHeight="1">
+    <row r="460" ht="20.25" customHeight="1">
       <c r="A460" s="8">
         <v>1539.0</v>
       </c>
@@ -55786,7 +55785,7 @@
       <c r="AW461" s="7"/>
       <c r="AX461" s="7"/>
     </row>
-    <row r="462" ht="20.25" hidden="1" customHeight="1">
+    <row r="462" ht="20.25" customHeight="1">
       <c r="A462" s="8">
         <v>1541.0</v>
       </c>
@@ -55894,7 +55893,7 @@
       <c r="AW462" s="7"/>
       <c r="AX462" s="7"/>
     </row>
-    <row r="463" ht="20.25" hidden="1" customHeight="1">
+    <row r="463" ht="20.25" customHeight="1">
       <c r="A463" s="12">
         <v>1542.0</v>
       </c>
@@ -56002,7 +56001,7 @@
       <c r="AW463" s="7"/>
       <c r="AX463" s="7"/>
     </row>
-    <row r="464" ht="20.25" hidden="1" customHeight="1">
+    <row r="464" ht="20.25" customHeight="1">
       <c r="A464" s="8">
         <v>1543.0</v>
       </c>
@@ -56110,7 +56109,7 @@
       <c r="AW464" s="7"/>
       <c r="AX464" s="7"/>
     </row>
-    <row r="465" ht="20.25" hidden="1" customHeight="1">
+    <row r="465" ht="20.25" customHeight="1">
       <c r="A465" s="12">
         <v>1544.0</v>
       </c>
@@ -56218,7 +56217,7 @@
       <c r="AW465" s="7"/>
       <c r="AX465" s="7"/>
     </row>
-    <row r="466" ht="20.25" hidden="1" customHeight="1">
+    <row r="466" ht="20.25" customHeight="1">
       <c r="A466" s="8">
         <v>1545.0</v>
       </c>
@@ -61527,13 +61526,7 @@
       <c r="AX566" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$AD$466">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="KC Batusangkar"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="$A$1:$AD$466"/>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
